--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R6aae28413acf4126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R7f15bf14a59c4828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R0a679ddf13e64776"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R60a7d81011d447c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R5b841beb61174cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R0af5f3541a8e4d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R4bd314e69efb4416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Rac6cccebf3a64f04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Rd9fdbff360a44385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R1337011038634222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R6502275b6b1544be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R004a296d84704eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R28e70792fa594710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R537ae36f09244e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Ra67ac35f92bc4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rcbeaa0772bbc45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rb39f4562100640d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Ra60d768884f346c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R67742729c6db4a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rb04c7c0b201641a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13714,7 +13714,7 @@
       <x:c r="K298"/>
       <x:c r="L298"/>
       <x:c r="M298" t="str">
-        <x:v>外-</x:v>
+        <x:v>外-16</x:v>
       </x:c>
       <x:c r="N298"/>
       <x:c r="O298"/>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R0349804f140f4042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rad2b095dee094a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R1d76e5b2d37b4251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Ra8bc4aa590184c6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R049b42411e9d4ef4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Ra835d2f2329640cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rde086491d7fa45c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Rcef11ae0a546421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Ra551e4ba175d44f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R433a993d0fc446fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R9f94ddc77ac34784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R9bc0a66d225c448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R6c66fdc5cf774b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R1f8101d8def34080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R47a1cc45d6b24d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R14792cc1f3014017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rf4cfdf8c11104ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R49a8a952c6344fa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R25bb6dd509384679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R3897452f7978465a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3815,7 +3815,7 @@
       </x:c>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:v>K-</x:v>
+        <x:v>K-49</x:v>
       </x:c>
       <x:c r="J54"/>
       <x:c r="K54"/>
@@ -9597,7 +9597,7 @@
       </x:c>
       <x:c r="H194"/>
       <x:c r="I194" t="str">
-        <x:v>K-51</x:v>
+        <x:v>K-52</x:v>
       </x:c>
       <x:c r="J194"/>
       <x:c r="K194"/>
@@ -9637,7 +9637,7 @@
       </x:c>
       <x:c r="H195"/>
       <x:c r="I195" t="str">
-        <x:v>K-52</x:v>
+        <x:v>K-53</x:v>
       </x:c>
       <x:c r="J195"/>
       <x:c r="K195"/>
@@ -9717,7 +9717,7 @@
         <x:v>K-47</x:v>
       </x:c>
       <x:c r="I197" t="str">
-        <x:v>K-54</x:v>
+        <x:v>K-55</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>K-28</x:v>
@@ -9765,7 +9765,7 @@
         <x:v>K-48</x:v>
       </x:c>
       <x:c r="I198" t="str">
-        <x:v>K-55</x:v>
+        <x:v>K-56</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>K-29</x:v>
@@ -9967,7 +9967,7 @@
       </x:c>
       <x:c r="H203"/>
       <x:c r="I203" t="str">
-        <x:v>K-53</x:v>
+        <x:v>K-54</x:v>
       </x:c>
       <x:c r="J203"/>
       <x:c r="K203"/>
@@ -13651,7 +13651,7 @@
       </x:c>
       <x:c r="H295"/>
       <x:c r="I295" t="str">
-        <x:v>K-50</x:v>
+        <x:v>K-51</x:v>
       </x:c>
       <x:c r="J295"/>
       <x:c r="K295"/>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -9911,29 +9911,33 @@
     </x:row>
     <x:row r="202" ht="21" customHeight="1">
       <x:c r="A202" t="str">
-        <x:v>上ノ庄</x:v>
+        <x:v>安場</x:v>
       </x:c>
       <x:c r="B202" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>介護</x:v>
       </x:c>
       <x:c r="C202" t="n">
         <x:v>203</x:v>
       </x:c>
       <x:c r="D202" t="n">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E202" t="str">
-        <x:v>東研サーモテック</x:v>
+        <x:v>グループホームあんだんて</x:v>
       </x:c>
       <x:c r="F202"/>
       <x:c r="G202" t="str">
-        <x:v>63-5321</x:v>
+        <x:v>39-1900　</x:v>
       </x:c>
       <x:c r="H202"/>
-      <x:c r="I202"/>
+      <x:c r="I202" t="str">
+        <x:v>K-54</x:v>
+      </x:c>
       <x:c r="J202"/>
       <x:c r="K202"/>
-      <x:c r="L202"/>
+      <x:c r="L202" t="str">
+        <x:v>K-51</x:v>
+      </x:c>
       <x:c r="M202"/>
       <x:c r="N202"/>
       <x:c r="O202"/>
@@ -9947,32 +9951,30 @@
     </x:row>
     <x:row r="203" ht="21" customHeight="1">
       <x:c r="A203" t="str">
-        <x:v>安場</x:v>
+        <x:v>白樫</x:v>
       </x:c>
       <x:c r="B203" t="str">
-        <x:v>介護</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C203" t="n">
         <x:v>204</x:v>
       </x:c>
       <x:c r="D203" t="n">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E203" t="str">
-        <x:v>グループホームあんだんて</x:v>
+        <x:v>福田工業㈱</x:v>
       </x:c>
       <x:c r="F203"/>
-      <x:c r="G203" t="str">
-        <x:v>39-1900　</x:v>
-      </x:c>
+      <x:c r="G203"/>
       <x:c r="H203"/>
       <x:c r="I203" t="str">
-        <x:v>K-54</x:v>
+        <x:v>K-37</x:v>
       </x:c>
       <x:c r="J203"/>
       <x:c r="K203"/>
       <x:c r="L203" t="str">
-        <x:v>K-51</x:v>
+        <x:v>K-36</x:v>
       </x:c>
       <x:c r="M203"/>
       <x:c r="N203"/>
@@ -9990,28 +9992,30 @@
         <x:v>白樫</x:v>
       </x:c>
       <x:c r="B204" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C204" t="n">
         <x:v>205</x:v>
       </x:c>
       <x:c r="D204" t="n">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E204" t="str">
-        <x:v>福田工業㈱</x:v>
+        <x:v>ノアーズアーク</x:v>
       </x:c>
       <x:c r="F204"/>
-      <x:c r="G204"/>
-      <x:c r="H204"/>
-      <x:c r="I204" t="str">
-        <x:v>K-37</x:v>
-      </x:c>
+      <x:c r="G204" t="str">
+        <x:v>65-9898</x:v>
+      </x:c>
+      <x:c r="H204" t="str">
+        <x:v>K-43</x:v>
+      </x:c>
+      <x:c r="I204"/>
       <x:c r="J204"/>
-      <x:c r="K204"/>
-      <x:c r="L204" t="str">
-        <x:v>K-36</x:v>
-      </x:c>
+      <x:c r="K204" t="str">
+        <x:v>K-9</x:v>
+      </x:c>
+      <x:c r="L204"/>
       <x:c r="M204"/>
       <x:c r="N204"/>
       <x:c r="O204"/>
@@ -10019,7 +10023,9 @@
       <x:c r="Q204"/>
       <x:c r="R204"/>
       <x:c r="S204"/>
-      <x:c r="T204"/>
+      <x:c r="T204" t="str">
+        <x:v>大栄中村</x:v>
+      </x:c>
       <x:c r="U204"/>
       <x:c r="V204"/>
     </x:row>
@@ -10028,30 +10034,32 @@
         <x:v>白樫</x:v>
       </x:c>
       <x:c r="B205" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C205" t="n">
         <x:v>206</x:v>
       </x:c>
       <x:c r="D205" t="n">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E205" t="str">
-        <x:v>ノアーズアーク</x:v>
+        <x:v>ク ラ コ</x:v>
       </x:c>
       <x:c r="F205"/>
       <x:c r="G205" t="str">
-        <x:v>65-9898</x:v>
+        <x:v>24-3221</x:v>
       </x:c>
       <x:c r="H205" t="str">
-        <x:v>K-43</x:v>
+        <x:v>K-44</x:v>
       </x:c>
       <x:c r="I205"/>
-      <x:c r="J205"/>
-      <x:c r="K205" t="str">
-        <x:v>K-9</x:v>
-      </x:c>
-      <x:c r="L205"/>
+      <x:c r="J205" t="str">
+        <x:v>K-31</x:v>
+      </x:c>
+      <x:c r="K205"/>
+      <x:c r="L205" t="str">
+        <x:v>K-40</x:v>
+      </x:c>
       <x:c r="M205"/>
       <x:c r="N205"/>
       <x:c r="O205"/>
@@ -10059,9 +10067,7 @@
       <x:c r="Q205"/>
       <x:c r="R205"/>
       <x:c r="S205"/>
-      <x:c r="T205" t="str">
-        <x:v>大栄中村</x:v>
-      </x:c>
+      <x:c r="T205"/>
       <x:c r="U205"/>
       <x:c r="V205"/>
     </x:row>
@@ -10076,25 +10082,25 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="D206" t="n">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E206" t="str">
-        <x:v>ク ラ コ</x:v>
-      </x:c>
-      <x:c r="F206"/>
+        <x:v>飯田金属工業</x:v>
+      </x:c>
+      <x:c r="F206" t="str">
+        <x:v>計量</x:v>
+      </x:c>
       <x:c r="G206" t="str">
-        <x:v>24-3221</x:v>
-      </x:c>
-      <x:c r="H206" t="str">
-        <x:v>K-44</x:v>
-      </x:c>
-      <x:c r="I206"/>
-      <x:c r="J206" t="str">
-        <x:v>K-31</x:v>
-      </x:c>
+        <x:v>24-5050</x:v>
+      </x:c>
+      <x:c r="H206"/>
+      <x:c r="I206" t="str">
+        <x:v>K-39</x:v>
+      </x:c>
+      <x:c r="J206"/>
       <x:c r="K206"/>
       <x:c r="L206" t="str">
-        <x:v>K-40</x:v>
+        <x:v>K-38</x:v>
       </x:c>
       <x:c r="M206"/>
       <x:c r="N206"/>
@@ -10118,25 +10124,19 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="D207" t="n">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E207" t="str">
-        <x:v>飯田金属工業</x:v>
-      </x:c>
-      <x:c r="F207" t="str">
-        <x:v>計量</x:v>
-      </x:c>
-      <x:c r="G207" t="str">
-        <x:v>24-5050</x:v>
-      </x:c>
+        <x:v>遊士屋</x:v>
+      </x:c>
+      <x:c r="F207"/>
+      <x:c r="G207"/>
       <x:c r="H207"/>
-      <x:c r="I207" t="str">
-        <x:v>K-39</x:v>
-      </x:c>
+      <x:c r="I207"/>
       <x:c r="J207"/>
       <x:c r="K207"/>
       <x:c r="L207" t="str">
-        <x:v>K-38</x:v>
+        <x:v>K-43</x:v>
       </x:c>
       <x:c r="M207"/>
       <x:c r="N207"/>
@@ -10151,7 +10151,7 @@
     </x:row>
     <x:row r="208" ht="21" customHeight="1">
       <x:c r="A208" t="str">
-        <x:v>白樫</x:v>
+        <x:v>白樫 </x:v>
       </x:c>
       <x:c r="B208" t="str">
         <x:v>会社　商店</x:v>
@@ -10160,19 +10160,23 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="D208" t="n">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E208" t="str">
-        <x:v>遊士屋</x:v>
-      </x:c>
-      <x:c r="F208"/>
+        <x:v>やさいの戸島屋</x:v>
+      </x:c>
+      <x:c r="F208" t="str">
+        <x:v>計量</x:v>
+      </x:c>
       <x:c r="G208"/>
       <x:c r="H208"/>
-      <x:c r="I208"/>
+      <x:c r="I208" t="str">
+        <x:v>K-38</x:v>
+      </x:c>
       <x:c r="J208"/>
       <x:c r="K208"/>
       <x:c r="L208" t="str">
-        <x:v>K-43</x:v>
+        <x:v>K-37</x:v>
       </x:c>
       <x:c r="M208"/>
       <x:c r="N208"/>
@@ -10196,23 +10200,21 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="D209" t="n">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E209" t="str">
-        <x:v>やさいの戸島屋</x:v>
-      </x:c>
-      <x:c r="F209" t="str">
-        <x:v>計量</x:v>
-      </x:c>
-      <x:c r="G209"/>
+        <x:v>大村紙業</x:v>
+      </x:c>
+      <x:c r="F209"/>
+      <x:c r="G209" t="str">
+        <x:v>20-1326</x:v>
+      </x:c>
       <x:c r="H209"/>
-      <x:c r="I209" t="str">
-        <x:v>K-38</x:v>
-      </x:c>
+      <x:c r="I209"/>
       <x:c r="J209"/>
       <x:c r="K209"/>
       <x:c r="L209" t="str">
-        <x:v>K-37</x:v>
+        <x:v>K-41</x:v>
       </x:c>
       <x:c r="M209"/>
       <x:c r="N209"/>
@@ -10236,21 +10238,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="D210" t="n">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E210" t="str">
-        <x:v>大村紙業</x:v>
+        <x:v>スミロン</x:v>
       </x:c>
       <x:c r="F210"/>
-      <x:c r="G210" t="str">
-        <x:v>20-1326</x:v>
-      </x:c>
+      <x:c r="G210"/>
       <x:c r="H210"/>
       <x:c r="I210"/>
       <x:c r="J210"/>
       <x:c r="K210"/>
       <x:c r="L210" t="str">
-        <x:v>K-41</x:v>
+        <x:v>K-39</x:v>
       </x:c>
       <x:c r="M210"/>
       <x:c r="N210"/>
@@ -10274,19 +10274,21 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="D211" t="n">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E211" t="str">
-        <x:v>スミロン</x:v>
+        <x:v>ミナルコ</x:v>
       </x:c>
       <x:c r="F211"/>
-      <x:c r="G211"/>
+      <x:c r="G211" t="str">
+        <x:v>20-1201</x:v>
+      </x:c>
       <x:c r="H211"/>
       <x:c r="I211"/>
       <x:c r="J211"/>
       <x:c r="K211"/>
       <x:c r="L211" t="str">
-        <x:v>K-39</x:v>
+        <x:v>K-42</x:v>
       </x:c>
       <x:c r="M211"/>
       <x:c r="N211"/>
@@ -10310,21 +10312,23 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="D212" t="n">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E212" t="str">
-        <x:v>ミナルコ</x:v>
-      </x:c>
-      <x:c r="F212"/>
+        <x:v>チョーヤ梅酒</x:v>
+      </x:c>
+      <x:c r="F212" t="str">
+        <x:v>計量</x:v>
+      </x:c>
       <x:c r="G212" t="str">
-        <x:v>20-1201</x:v>
+        <x:v>20-2255</x:v>
       </x:c>
       <x:c r="H212"/>
       <x:c r="I212"/>
       <x:c r="J212"/>
       <x:c r="K212"/>
       <x:c r="L212" t="str">
-        <x:v>K-42</x:v>
+        <x:v>K-44</x:v>
       </x:c>
       <x:c r="M212"/>
       <x:c r="N212"/>
@@ -10348,24 +10352,24 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="D213" t="n">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E213" t="str">
-        <x:v>チョーヤ梅酒</x:v>
-      </x:c>
-      <x:c r="F213" t="str">
-        <x:v>計量</x:v>
-      </x:c>
+        <x:v>ヤシマナダ三重工場</x:v>
+      </x:c>
+      <x:c r="F213"/>
       <x:c r="G213" t="str">
-        <x:v>20-2255</x:v>
-      </x:c>
-      <x:c r="H213"/>
+        <x:v>20-1155</x:v>
+      </x:c>
+      <x:c r="H213" t="str">
+        <x:v>K-50</x:v>
+      </x:c>
       <x:c r="I213"/>
       <x:c r="J213"/>
-      <x:c r="K213"/>
-      <x:c r="L213" t="str">
-        <x:v>K-44</x:v>
-      </x:c>
+      <x:c r="K213" t="str">
+        <x:v>K-43</x:v>
+      </x:c>
+      <x:c r="L213"/>
       <x:c r="M213"/>
       <x:c r="N213"/>
       <x:c r="O213"/>
@@ -10388,24 +10392,20 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="D214" t="n">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E214" t="str">
-        <x:v>ヤシマナダ三重工場</x:v>
+        <x:v>大阪バネ工業</x:v>
       </x:c>
       <x:c r="F214"/>
-      <x:c r="G214" t="str">
-        <x:v>20-1155</x:v>
-      </x:c>
-      <x:c r="H214" t="str">
-        <x:v>K-50</x:v>
-      </x:c>
+      <x:c r="G214"/>
+      <x:c r="H214"/>
       <x:c r="I214"/>
       <x:c r="J214"/>
-      <x:c r="K214" t="str">
-        <x:v>K-43</x:v>
-      </x:c>
-      <x:c r="L214"/>
+      <x:c r="K214"/>
+      <x:c r="L214" t="str">
+        <x:v>K-57</x:v>
+      </x:c>
       <x:c r="M214"/>
       <x:c r="N214"/>
       <x:c r="O214"/>
@@ -10419,29 +10419,33 @@
     </x:row>
     <x:row r="215" ht="21" customHeight="1">
       <x:c r="A215" t="str">
-        <x:v>白樫 </x:v>
+        <x:v>治田</x:v>
       </x:c>
       <x:c r="B215" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>車 ガソリン</x:v>
       </x:c>
       <x:c r="C215" t="n">
         <x:v>216</x:v>
       </x:c>
       <x:c r="D215" t="n">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E215" t="str">
-        <x:v>大阪バネ工業</x:v>
+        <x:v>一光　治田</x:v>
       </x:c>
       <x:c r="F215"/>
-      <x:c r="G215"/>
+      <x:c r="G215" t="str">
+        <x:v>20-1196</x:v>
+      </x:c>
       <x:c r="H215"/>
       <x:c r="I215"/>
-      <x:c r="J215"/>
-      <x:c r="K215"/>
-      <x:c r="L215" t="str">
-        <x:v>K-57</x:v>
-      </x:c>
+      <x:c r="J215" t="str">
+        <x:v>　</x:v>
+      </x:c>
+      <x:c r="K215" t="str">
+        <x:v>K-6</x:v>
+      </x:c>
+      <x:c r="L215"/>
       <x:c r="M215"/>
       <x:c r="N215"/>
       <x:c r="O215"/>
@@ -10458,30 +10462,28 @@
         <x:v>治田</x:v>
       </x:c>
       <x:c r="B216" t="str">
-        <x:v>車 ガソリン</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C216" t="n">
         <x:v>217</x:v>
       </x:c>
       <x:c r="D216" t="n">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E216" t="str">
-        <x:v>一光　治田</x:v>
+        <x:v>福田工業 治田工場</x:v>
       </x:c>
       <x:c r="F216"/>
-      <x:c r="G216" t="str">
-        <x:v>20-1196</x:v>
-      </x:c>
+      <x:c r="G216"/>
       <x:c r="H216"/>
-      <x:c r="I216"/>
-      <x:c r="J216" t="str">
-        <x:v>　</x:v>
-      </x:c>
-      <x:c r="K216" t="str">
-        <x:v>K-6</x:v>
-      </x:c>
-      <x:c r="L216"/>
+      <x:c r="I216" t="str">
+        <x:v>K-40</x:v>
+      </x:c>
+      <x:c r="J216"/>
+      <x:c r="K216"/>
+      <x:c r="L216" t="str">
+        <x:v>K-35</x:v>
+      </x:c>
       <x:c r="M216"/>
       <x:c r="N216"/>
       <x:c r="O216"/>
@@ -10504,21 +10506,25 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="D217" t="n">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E217" t="str">
-        <x:v>福田工業 治田工場</x:v>
+        <x:v>瀬戸川原花苑</x:v>
       </x:c>
       <x:c r="F217"/>
-      <x:c r="G217"/>
-      <x:c r="H217"/>
-      <x:c r="I217" t="str">
-        <x:v>K-40</x:v>
-      </x:c>
-      <x:c r="J217"/>
+      <x:c r="G217" t="str">
+        <x:v>20-9777</x:v>
+      </x:c>
+      <x:c r="H217" t="str">
+        <x:v>K-49</x:v>
+      </x:c>
+      <x:c r="I217"/>
+      <x:c r="J217" t="str">
+        <x:v>K-32</x:v>
+      </x:c>
       <x:c r="K217"/>
       <x:c r="L217" t="str">
-        <x:v>K-35</x:v>
+        <x:v>K-50</x:v>
       </x:c>
       <x:c r="M217"/>
       <x:c r="N217"/>
@@ -10542,26 +10548,22 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="D218" t="n">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E218" t="str">
-        <x:v>瀬戸川原花苑</x:v>
+        <x:v>大同工業</x:v>
       </x:c>
       <x:c r="F218"/>
       <x:c r="G218" t="str">
-        <x:v>20-9777</x:v>
-      </x:c>
-      <x:c r="H218" t="str">
-        <x:v>K-49</x:v>
-      </x:c>
+        <x:v>20-1818</x:v>
+      </x:c>
+      <x:c r="H218"/>
       <x:c r="I218"/>
-      <x:c r="J218" t="str">
-        <x:v>K-32</x:v>
-      </x:c>
-      <x:c r="K218"/>
-      <x:c r="L218" t="str">
-        <x:v>K-50</x:v>
-      </x:c>
+      <x:c r="J218"/>
+      <x:c r="K218" t="str">
+        <x:v>K-7</x:v>
+      </x:c>
+      <x:c r="L218"/>
       <x:c r="M218"/>
       <x:c r="N218"/>
       <x:c r="O218"/>
@@ -10584,20 +10586,20 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="D219" t="n">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E219" t="str">
-        <x:v>大同工業</x:v>
+        <x:v>錦城ゴム</x:v>
       </x:c>
       <x:c r="F219"/>
       <x:c r="G219" t="str">
-        <x:v>20-1818</x:v>
+        <x:v>20-1857</x:v>
       </x:c>
       <x:c r="H219"/>
       <x:c r="I219"/>
       <x:c r="J219"/>
       <x:c r="K219" t="str">
-        <x:v>K-7</x:v>
+        <x:v>K-8</x:v>
       </x:c>
       <x:c r="L219"/>
       <x:c r="M219"/>
@@ -10616,28 +10618,30 @@
         <x:v>治田</x:v>
       </x:c>
       <x:c r="B220" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>介護</x:v>
       </x:c>
       <x:c r="C220" t="n">
         <x:v>221</x:v>
       </x:c>
       <x:c r="D220" t="n">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E220" t="str">
-        <x:v>錦城ゴム</x:v>
+        <x:v>梨の木園</x:v>
       </x:c>
       <x:c r="F220"/>
-      <x:c r="G220" t="str">
-        <x:v>20-1857</x:v>
-      </x:c>
-      <x:c r="H220"/>
+      <x:c r="G220"/>
+      <x:c r="H220" t="str">
+        <x:v>K-42</x:v>
+      </x:c>
       <x:c r="I220"/>
-      <x:c r="J220"/>
-      <x:c r="K220" t="str">
-        <x:v>K-8</x:v>
-      </x:c>
-      <x:c r="L220"/>
+      <x:c r="J220" t="str">
+        <x:v>K-30</x:v>
+      </x:c>
+      <x:c r="K220"/>
+      <x:c r="L220" t="str">
+        <x:v>K-45</x:v>
+      </x:c>
       <x:c r="M220"/>
       <x:c r="N220"/>
       <x:c r="O220"/>
@@ -10654,30 +10658,26 @@
         <x:v>治田</x:v>
       </x:c>
       <x:c r="B221" t="str">
-        <x:v>介護</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C221" t="n">
         <x:v>222</x:v>
       </x:c>
       <x:c r="D221" t="n">
-        <x:v>215</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E221" t="str">
-        <x:v>梨の木園</x:v>
+        <x:v>伊賀　アスコン</x:v>
       </x:c>
       <x:c r="F221"/>
       <x:c r="G221"/>
-      <x:c r="H221" t="str">
-        <x:v>K-42</x:v>
-      </x:c>
+      <x:c r="H221"/>
       <x:c r="I221"/>
       <x:c r="J221" t="str">
-        <x:v>K-30</x:v>
+        <x:v>K-33</x:v>
       </x:c>
       <x:c r="K221"/>
-      <x:c r="L221" t="str">
-        <x:v>K-45</x:v>
-      </x:c>
+      <x:c r="L221"/>
       <x:c r="M221"/>
       <x:c r="N221"/>
       <x:c r="O221"/>
@@ -10691,7 +10691,7 @@
     </x:row>
     <x:row r="222" ht="21" customHeight="1">
       <x:c r="A222" t="str">
-        <x:v>治田</x:v>
+        <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B222" t="str">
         <x:v>会社　商店</x:v>
@@ -10700,20 +10700,24 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="D222" t="n">
-        <x:v>295</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E222" t="str">
-        <x:v>伊賀　アスコン</x:v>
+        <x:v>豊正</x:v>
       </x:c>
       <x:c r="F222"/>
-      <x:c r="G222"/>
+      <x:c r="G222" t="str">
+        <x:v>24-2712</x:v>
+      </x:c>
       <x:c r="H222"/>
-      <x:c r="I222"/>
-      <x:c r="J222" t="str">
-        <x:v>K-33</x:v>
-      </x:c>
+      <x:c r="I222" t="str">
+        <x:v>K-46</x:v>
+      </x:c>
+      <x:c r="J222"/>
       <x:c r="K222"/>
-      <x:c r="L222"/>
+      <x:c r="L222" t="str">
+        <x:v>K-28</x:v>
+      </x:c>
       <x:c r="M222"/>
       <x:c r="N222"/>
       <x:c r="O222"/>
@@ -10730,30 +10734,28 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B223" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>郵便局</x:v>
       </x:c>
       <x:c r="C223" t="n">
         <x:v>224</x:v>
       </x:c>
       <x:c r="D223" t="n">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E223" t="str">
-        <x:v>豊正</x:v>
+        <x:v>岩倉郵便局</x:v>
       </x:c>
       <x:c r="F223"/>
       <x:c r="G223" t="str">
-        <x:v>24-2712</x:v>
+        <x:v>21-4296</x:v>
       </x:c>
       <x:c r="H223"/>
-      <x:c r="I223" t="str">
-        <x:v>K-46</x:v>
-      </x:c>
+      <x:c r="I223"/>
       <x:c r="J223"/>
-      <x:c r="K223"/>
-      <x:c r="L223" t="str">
-        <x:v>K-28</x:v>
-      </x:c>
+      <x:c r="K223" t="str">
+        <x:v>K-30</x:v>
+      </x:c>
+      <x:c r="L223"/>
       <x:c r="M223"/>
       <x:c r="N223"/>
       <x:c r="O223"/>
@@ -10770,28 +10772,30 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B224" t="str">
-        <x:v>郵便局</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C224" t="n">
         <x:v>225</x:v>
       </x:c>
       <x:c r="D224" t="n">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E224" t="str">
-        <x:v>岩倉郵便局</x:v>
+        <x:v>ふる里</x:v>
       </x:c>
       <x:c r="F224"/>
       <x:c r="G224" t="str">
-        <x:v>21-4296</x:v>
+        <x:v>21-4498</x:v>
       </x:c>
       <x:c r="H224"/>
-      <x:c r="I224"/>
+      <x:c r="I224" t="str">
+        <x:v>K-45</x:v>
+      </x:c>
       <x:c r="J224"/>
-      <x:c r="K224" t="str">
-        <x:v>K-30</x:v>
-      </x:c>
-      <x:c r="L224"/>
+      <x:c r="K224"/>
+      <x:c r="L224" t="str">
+        <x:v>K-29</x:v>
+      </x:c>
       <x:c r="M224"/>
       <x:c r="N224"/>
       <x:c r="O224"/>
@@ -10808,36 +10812,40 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B225" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>スポーツ</x:v>
       </x:c>
       <x:c r="C225" t="n">
         <x:v>226</x:v>
       </x:c>
       <x:c r="D225" t="n">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E225" t="str">
-        <x:v>ふる里</x:v>
+        <x:v>島ヶ原ゴルフ</x:v>
       </x:c>
       <x:c r="F225"/>
       <x:c r="G225" t="str">
-        <x:v>21-4498</x:v>
+        <x:v>59-3111</x:v>
       </x:c>
       <x:c r="H225"/>
       <x:c r="I225" t="str">
-        <x:v>K-45</x:v>
+        <x:v>K-41</x:v>
       </x:c>
       <x:c r="J225"/>
       <x:c r="K225"/>
       <x:c r="L225" t="str">
-        <x:v>K-29</x:v>
+        <x:v>K-33</x:v>
       </x:c>
       <x:c r="M225"/>
       <x:c r="N225"/>
       <x:c r="O225"/>
-      <x:c r="P225"/>
+      <x:c r="P225" t="str">
+        <x:v>金属-61</x:v>
+      </x:c>
       <x:c r="Q225"/>
-      <x:c r="R225"/>
+      <x:c r="R225" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S225"/>
       <x:c r="T225"/>
       <x:c r="U225"/>
@@ -10848,40 +10856,36 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B226" t="str">
-        <x:v>スポーツ</x:v>
+        <x:v>郵便局</x:v>
       </x:c>
       <x:c r="C226" t="n">
         <x:v>227</x:v>
       </x:c>
       <x:c r="D226" t="n">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E226" t="str">
-        <x:v>島ヶ原ゴルフ</x:v>
+        <x:v>島ヶ原郵便局</x:v>
       </x:c>
       <x:c r="F226"/>
       <x:c r="G226" t="str">
-        <x:v>59-3111</x:v>
+        <x:v>59-2500</x:v>
       </x:c>
       <x:c r="H226"/>
       <x:c r="I226" t="str">
-        <x:v>K-41</x:v>
+        <x:v>K-43</x:v>
       </x:c>
       <x:c r="J226"/>
       <x:c r="K226"/>
       <x:c r="L226" t="str">
-        <x:v>K-33</x:v>
+        <x:v>K-31</x:v>
       </x:c>
       <x:c r="M226"/>
       <x:c r="N226"/>
       <x:c r="O226"/>
-      <x:c r="P226" t="str">
-        <x:v>金属-61</x:v>
-      </x:c>
+      <x:c r="P226"/>
       <x:c r="Q226"/>
-      <x:c r="R226" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R226"/>
       <x:c r="S226"/>
       <x:c r="T226"/>
       <x:c r="U226"/>
@@ -10892,29 +10896,29 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B227" t="str">
-        <x:v>郵便局</x:v>
+        <x:v>病院　薬</x:v>
       </x:c>
       <x:c r="C227" t="n">
         <x:v>228</x:v>
       </x:c>
       <x:c r="D227" t="n">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E227" t="str">
-        <x:v>島ヶ原郵便局</x:v>
+        <x:v>フラワー薬局　島ヶ原</x:v>
       </x:c>
       <x:c r="F227"/>
       <x:c r="G227" t="str">
-        <x:v>59-2500</x:v>
+        <x:v>59-9311</x:v>
       </x:c>
       <x:c r="H227"/>
       <x:c r="I227" t="str">
-        <x:v>K-43</x:v>
+        <x:v>K-42</x:v>
       </x:c>
       <x:c r="J227"/>
       <x:c r="K227"/>
       <x:c r="L227" t="str">
-        <x:v>K-31</x:v>
+        <x:v>K-32</x:v>
       </x:c>
       <x:c r="M227"/>
       <x:c r="N227"/>
@@ -10932,40 +10936,46 @@
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B228" t="str">
-        <x:v>病院　薬</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C228" t="n">
         <x:v>229</x:v>
       </x:c>
       <x:c r="D228" t="n">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E228" t="str">
-        <x:v>フラワー薬局　島ヶ原</x:v>
+        <x:v>OKキャンプ</x:v>
       </x:c>
       <x:c r="F228"/>
       <x:c r="G228" t="str">
-        <x:v>59-9311</x:v>
-      </x:c>
-      <x:c r="H228"/>
-      <x:c r="I228" t="str">
-        <x:v>K-42</x:v>
-      </x:c>
+        <x:v>59-2079</x:v>
+      </x:c>
+      <x:c r="H228" t="str">
+        <x:v>K-40</x:v>
+      </x:c>
+      <x:c r="I228"/>
       <x:c r="J228"/>
       <x:c r="K228"/>
-      <x:c r="L228" t="str">
-        <x:v>K-32</x:v>
-      </x:c>
+      <x:c r="L228"/>
       <x:c r="M228"/>
       <x:c r="N228"/>
       <x:c r="O228"/>
-      <x:c r="P228"/>
+      <x:c r="P228" t="str">
+        <x:v>金属-60</x:v>
+      </x:c>
       <x:c r="Q228"/>
-      <x:c r="R228"/>
+      <x:c r="R228" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S228"/>
-      <x:c r="T228"/>
+      <x:c r="T228" t="str">
+        <x:v>夏休み中月金</x:v>
+      </x:c>
       <x:c r="U228"/>
-      <x:c r="V228"/>
+      <x:c r="V228" t="str">
+        <x:v>3月～11月</x:v>
+      </x:c>
     </x:row>
     <x:row r="229" ht="21" customHeight="1">
       <x:c r="A229" t="str">
@@ -10978,128 +10988,122 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="D229" t="n">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E229" t="str">
-        <x:v>OKキャンプ</x:v>
+        <x:v>やぶっちゃらんど</x:v>
       </x:c>
       <x:c r="F229"/>
       <x:c r="G229" t="str">
-        <x:v>59-2079</x:v>
+        <x:v>59-3939</x:v>
       </x:c>
       <x:c r="H229" t="str">
-        <x:v>K-40</x:v>
-      </x:c>
-      <x:c r="I229"/>
+        <x:v>K-39</x:v>
+      </x:c>
+      <x:c r="I229" t="str">
+        <x:v>K-44</x:v>
+      </x:c>
       <x:c r="J229"/>
-      <x:c r="K229"/>
-      <x:c r="L229"/>
-      <x:c r="M229"/>
+      <x:c r="K229" t="str">
+        <x:v>K-31</x:v>
+      </x:c>
+      <x:c r="L229" t="str">
+        <x:v>K-30</x:v>
+      </x:c>
+      <x:c r="M229" t="str">
+        <x:v>内-19</x:v>
+      </x:c>
       <x:c r="N229"/>
       <x:c r="O229"/>
       <x:c r="P229" t="str">
-        <x:v>金属-60</x:v>
+        <x:v>金属-59</x:v>
       </x:c>
       <x:c r="Q229"/>
       <x:c r="R229" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
       <x:c r="S229"/>
-      <x:c r="T229" t="str">
-        <x:v>夏休み中月金</x:v>
-      </x:c>
+      <x:c r="T229"/>
       <x:c r="U229"/>
-      <x:c r="V229" t="str">
-        <x:v>3月～11月</x:v>
-      </x:c>
+      <x:c r="V229"/>
     </x:row>
     <x:row r="230" ht="21" customHeight="1">
       <x:c r="A230" t="str">
         <x:v>島ヶ原</x:v>
       </x:c>
       <x:c r="B230" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C230" t="n">
         <x:v>231</x:v>
       </x:c>
       <x:c r="D230" t="n">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E230" t="str">
-        <x:v>やぶっちゃらんど</x:v>
+        <x:v>株式会社　MCS</x:v>
       </x:c>
       <x:c r="F230"/>
-      <x:c r="G230" t="str">
-        <x:v>59-3939</x:v>
-      </x:c>
-      <x:c r="H230" t="str">
-        <x:v>K-39</x:v>
-      </x:c>
-      <x:c r="I230" t="str">
-        <x:v>K-44</x:v>
-      </x:c>
+      <x:c r="G230"/>
+      <x:c r="H230"/>
+      <x:c r="I230"/>
       <x:c r="J230"/>
-      <x:c r="K230" t="str">
-        <x:v>K-31</x:v>
-      </x:c>
+      <x:c r="K230"/>
       <x:c r="L230" t="str">
-        <x:v>K-30</x:v>
-      </x:c>
-      <x:c r="M230" t="str">
-        <x:v>内-19</x:v>
-      </x:c>
+        <x:v>K-34</x:v>
+      </x:c>
+      <x:c r="M230"/>
       <x:c r="N230"/>
       <x:c r="O230"/>
       <x:c r="P230" t="str">
-        <x:v>金属-59</x:v>
+        <x:v>金属-62</x:v>
       </x:c>
       <x:c r="Q230"/>
-      <x:c r="R230" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R230"/>
       <x:c r="S230"/>
-      <x:c r="T230"/>
+      <x:c r="T230" t="str">
+        <x:v>金属PETを一緒に運ぶ</x:v>
+      </x:c>
       <x:c r="U230"/>
       <x:c r="V230"/>
     </x:row>
     <x:row r="231" ht="21" customHeight="1">
       <x:c r="A231" t="str">
-        <x:v>島ヶ原</x:v>
+        <x:v>三田</x:v>
       </x:c>
       <x:c r="B231" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>介護</x:v>
       </x:c>
       <x:c r="C231" t="n">
         <x:v>232</x:v>
       </x:c>
       <x:c r="D231" t="n">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E231" t="str">
-        <x:v>株式会社　MCS</x:v>
+        <x:v>虹の家</x:v>
       </x:c>
       <x:c r="F231"/>
-      <x:c r="G231"/>
+      <x:c r="G231" t="str">
+        <x:v>26-6555</x:v>
+      </x:c>
       <x:c r="H231"/>
-      <x:c r="I231"/>
+      <x:c r="I231" t="str">
+        <x:v>K-48</x:v>
+      </x:c>
       <x:c r="J231"/>
       <x:c r="K231"/>
       <x:c r="L231" t="str">
-        <x:v>K-34</x:v>
+        <x:v>K-26</x:v>
       </x:c>
       <x:c r="M231"/>
       <x:c r="N231"/>
       <x:c r="O231"/>
-      <x:c r="P231" t="str">
-        <x:v>金属-62</x:v>
-      </x:c>
+      <x:c r="P231"/>
       <x:c r="Q231"/>
       <x:c r="R231"/>
       <x:c r="S231"/>
-      <x:c r="T231" t="str">
-        <x:v>金属PETを一緒に運ぶ</x:v>
-      </x:c>
+      <x:c r="T231"/>
       <x:c r="U231"/>
       <x:c r="V231"/>
     </x:row>
@@ -11108,29 +11112,29 @@
         <x:v>三田</x:v>
       </x:c>
       <x:c r="B232" t="str">
-        <x:v>介護</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C232" t="n">
         <x:v>233</x:v>
       </x:c>
       <x:c r="D232" t="n">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E232" t="str">
-        <x:v>虹の家</x:v>
+        <x:v>奥中　ブリーダー</x:v>
       </x:c>
       <x:c r="F232"/>
       <x:c r="G232" t="str">
-        <x:v>26-6555</x:v>
+        <x:v>備考欄</x:v>
       </x:c>
       <x:c r="H232"/>
       <x:c r="I232" t="str">
-        <x:v>K-48</x:v>
+        <x:v>K-47</x:v>
       </x:c>
       <x:c r="J232"/>
       <x:c r="K232"/>
       <x:c r="L232" t="str">
-        <x:v>K-26</x:v>
+        <x:v>K-27</x:v>
       </x:c>
       <x:c r="M232"/>
       <x:c r="N232"/>
@@ -11139,7 +11143,9 @@
       <x:c r="Q232"/>
       <x:c r="R232"/>
       <x:c r="S232"/>
-      <x:c r="T232"/>
+      <x:c r="T232" t="str">
+        <x:v>080-5162-6148</x:v>
+      </x:c>
       <x:c r="U232"/>
       <x:c r="V232"/>
     </x:row>
@@ -11154,34 +11160,32 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="D233" t="n">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E233" t="str">
-        <x:v>奥中　ブリーダー</x:v>
+        <x:v>リアルプロダクト</x:v>
       </x:c>
       <x:c r="F233"/>
       <x:c r="G233" t="str">
-        <x:v>備考欄</x:v>
+        <x:v>24-5471</x:v>
       </x:c>
       <x:c r="H233"/>
-      <x:c r="I233" t="str">
-        <x:v>K-47</x:v>
-      </x:c>
+      <x:c r="I233"/>
       <x:c r="J233"/>
-      <x:c r="K233"/>
-      <x:c r="L233" t="str">
-        <x:v>K-27</x:v>
-      </x:c>
+      <x:c r="K233" t="str">
+        <x:v>K-32</x:v>
+      </x:c>
+      <x:c r="L233"/>
       <x:c r="M233"/>
       <x:c r="N233"/>
       <x:c r="O233"/>
-      <x:c r="P233"/>
+      <x:c r="P233" t="str">
+        <x:v>金属-55</x:v>
+      </x:c>
       <x:c r="Q233"/>
       <x:c r="R233"/>
       <x:c r="S233"/>
-      <x:c r="T233" t="str">
-        <x:v>080-5162-6148</x:v>
-      </x:c>
+      <x:c r="T233"/>
       <x:c r="U233"/>
       <x:c r="V233"/>
     </x:row>
@@ -11190,34 +11194,34 @@
         <x:v>三田</x:v>
       </x:c>
       <x:c r="B234" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>新聞</x:v>
       </x:c>
       <x:c r="C234" t="n">
         <x:v>235</x:v>
       </x:c>
       <x:c r="D234" t="n">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E234" t="str">
-        <x:v>リアルプロダクト</x:v>
+        <x:v>中日三重サービス</x:v>
       </x:c>
       <x:c r="F234"/>
-      <x:c r="G234" t="str">
-        <x:v>24-5471</x:v>
-      </x:c>
-      <x:c r="H234"/>
+      <x:c r="G234"/>
+      <x:c r="H234" t="str">
+        <x:v>K-34</x:v>
+      </x:c>
       <x:c r="I234"/>
-      <x:c r="J234"/>
-      <x:c r="K234" t="str">
-        <x:v>K-32</x:v>
-      </x:c>
-      <x:c r="L234"/>
+      <x:c r="J234" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="K234"/>
+      <x:c r="L234" t="str">
+        <x:v>K-25</x:v>
+      </x:c>
       <x:c r="M234"/>
       <x:c r="N234"/>
       <x:c r="O234"/>
-      <x:c r="P234" t="str">
-        <x:v>金属-55</x:v>
-      </x:c>
+      <x:c r="P234"/>
       <x:c r="Q234"/>
       <x:c r="R234"/>
       <x:c r="S234"/>
@@ -11230,36 +11234,38 @@
         <x:v>三田</x:v>
       </x:c>
       <x:c r="B235" t="str">
-        <x:v>新聞</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C235" t="n">
         <x:v>236</x:v>
       </x:c>
       <x:c r="D235" t="n">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E235" t="str">
-        <x:v>中日三重サービス</x:v>
+        <x:v>三田マンション</x:v>
       </x:c>
       <x:c r="F235"/>
       <x:c r="G235"/>
       <x:c r="H235" t="str">
-        <x:v>K-34</x:v>
+        <x:v>K-36</x:v>
       </x:c>
       <x:c r="I235"/>
-      <x:c r="J235" t="str">
-        <x:v>M-</x:v>
-      </x:c>
-      <x:c r="K235"/>
-      <x:c r="L235" t="str">
-        <x:v>K-25</x:v>
-      </x:c>
+      <x:c r="J235"/>
+      <x:c r="K235" t="str">
+        <x:v>K-37</x:v>
+      </x:c>
+      <x:c r="L235"/>
       <x:c r="M235"/>
       <x:c r="N235"/>
       <x:c r="O235"/>
-      <x:c r="P235"/>
+      <x:c r="P235" t="str">
+        <x:v>金属-57</x:v>
+      </x:c>
       <x:c r="Q235"/>
-      <x:c r="R235"/>
+      <x:c r="R235" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S235"/>
       <x:c r="T235"/>
       <x:c r="U235"/>
@@ -11276,27 +11282,29 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="D236" t="n">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E236" t="str">
-        <x:v>三田マンション</x:v>
+        <x:v>エスペランザ</x:v>
       </x:c>
       <x:c r="F236"/>
-      <x:c r="G236"/>
+      <x:c r="G236" t="str">
+        <x:v>26-2625</x:v>
+      </x:c>
       <x:c r="H236" t="str">
-        <x:v>K-36</x:v>
+        <x:v>K-35</x:v>
       </x:c>
       <x:c r="I236"/>
       <x:c r="J236"/>
       <x:c r="K236" t="str">
-        <x:v>K-37</x:v>
+        <x:v>K-38</x:v>
       </x:c>
       <x:c r="L236"/>
       <x:c r="M236"/>
       <x:c r="N236"/>
       <x:c r="O236"/>
       <x:c r="P236" t="str">
-        <x:v>金属-57</x:v>
+        <x:v>金属-58</x:v>
       </x:c>
       <x:c r="Q236"/>
       <x:c r="R236" t="str">
@@ -11318,29 +11326,27 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="D237" t="n">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E237" t="str">
-        <x:v>エスペランザ</x:v>
+        <x:v>ドリームハイツ</x:v>
       </x:c>
       <x:c r="F237"/>
-      <x:c r="G237" t="str">
-        <x:v>26-2625</x:v>
-      </x:c>
+      <x:c r="G237"/>
       <x:c r="H237" t="str">
-        <x:v>K-35</x:v>
+        <x:v>K-37</x:v>
       </x:c>
       <x:c r="I237"/>
       <x:c r="J237"/>
       <x:c r="K237" t="str">
-        <x:v>K-38</x:v>
+        <x:v>K-35</x:v>
       </x:c>
       <x:c r="L237"/>
       <x:c r="M237"/>
       <x:c r="N237"/>
       <x:c r="O237"/>
       <x:c r="P237" t="str">
-        <x:v>金属-58</x:v>
+        <x:v>金属-56</x:v>
       </x:c>
       <x:c r="Q237"/>
       <x:c r="R237" t="str">
@@ -11362,32 +11368,28 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="D238" t="n">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E238" t="str">
-        <x:v>ドリームハイツ</x:v>
+        <x:v>桂ハイツ</x:v>
       </x:c>
       <x:c r="F238"/>
       <x:c r="G238"/>
       <x:c r="H238" t="str">
-        <x:v>K-37</x:v>
+        <x:v>K-38</x:v>
       </x:c>
       <x:c r="I238"/>
       <x:c r="J238"/>
       <x:c r="K238" t="str">
-        <x:v>K-35</x:v>
+        <x:v>K-36</x:v>
       </x:c>
       <x:c r="L238"/>
       <x:c r="M238"/>
       <x:c r="N238"/>
       <x:c r="O238"/>
-      <x:c r="P238" t="str">
-        <x:v>金属-56</x:v>
-      </x:c>
+      <x:c r="P238"/>
       <x:c r="Q238"/>
-      <x:c r="R238" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R238"/>
       <x:c r="S238"/>
       <x:c r="T238"/>
       <x:c r="U238"/>
@@ -11398,71 +11400,75 @@
         <x:v>三田</x:v>
       </x:c>
       <x:c r="B239" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C239" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="D239" t="n">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E239" t="str">
-        <x:v>桂ハイツ</x:v>
+        <x:v>ナカテック</x:v>
       </x:c>
       <x:c r="F239"/>
-      <x:c r="G239"/>
-      <x:c r="H239" t="str">
-        <x:v>K-38</x:v>
-      </x:c>
+      <x:c r="G239" t="str">
+        <x:v>26-7212</x:v>
+      </x:c>
+      <x:c r="H239"/>
       <x:c r="I239"/>
       <x:c r="J239"/>
       <x:c r="K239" t="str">
-        <x:v>K-36</x:v>
+        <x:v>K-34</x:v>
       </x:c>
       <x:c r="L239"/>
       <x:c r="M239"/>
       <x:c r="N239"/>
       <x:c r="O239"/>
-      <x:c r="P239"/>
+      <x:c r="P239" t="str">
+        <x:v>金属-54</x:v>
+      </x:c>
       <x:c r="Q239"/>
       <x:c r="R239"/>
       <x:c r="S239"/>
       <x:c r="T239"/>
       <x:c r="U239"/>
-      <x:c r="V239"/>
+      <x:c r="V239" t="str">
+        <x:v>金属1.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="240" ht="21" customHeight="1">
       <x:c r="A240" t="str">
         <x:v>三田</x:v>
       </x:c>
       <x:c r="B240" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>病院　薬</x:v>
       </x:c>
       <x:c r="C240" t="n">
         <x:v>241</x:v>
       </x:c>
       <x:c r="D240" t="n">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E240" t="str">
-        <x:v>ナカテック</x:v>
+        <x:v>メディﾂク</x:v>
       </x:c>
       <x:c r="F240"/>
       <x:c r="G240" t="str">
-        <x:v>26-7212</x:v>
+        <x:v>23-9436</x:v>
       </x:c>
       <x:c r="H240"/>
       <x:c r="I240"/>
       <x:c r="J240"/>
       <x:c r="K240" t="str">
-        <x:v>K-34</x:v>
+        <x:v>K-33</x:v>
       </x:c>
       <x:c r="L240"/>
       <x:c r="M240"/>
       <x:c r="N240"/>
       <x:c r="O240"/>
       <x:c r="P240" t="str">
-        <x:v>金属-54</x:v>
+        <x:v>金属-53</x:v>
       </x:c>
       <x:c r="Q240"/>
       <x:c r="R240"/>
@@ -11475,7 +11481,7 @@
     </x:row>
     <x:row r="241" ht="21" customHeight="1">
       <x:c r="A241" t="str">
-        <x:v>三田</x:v>
+        <x:v>車坂</x:v>
       </x:c>
       <x:c r="B241" t="str">
         <x:v>病院　薬</x:v>
@@ -11484,64 +11490,64 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="D241" t="n">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E241" t="str">
-        <x:v>メディﾂク</x:v>
+        <x:v>谷本整形</x:v>
       </x:c>
       <x:c r="F241"/>
       <x:c r="G241" t="str">
-        <x:v>23-9436</x:v>
-      </x:c>
-      <x:c r="H241"/>
+        <x:v>21-0934</x:v>
+      </x:c>
+      <x:c r="H241" t="str">
+        <x:v>H-55</x:v>
+      </x:c>
       <x:c r="I241"/>
       <x:c r="J241"/>
-      <x:c r="K241" t="str">
-        <x:v>K-33</x:v>
-      </x:c>
+      <x:c r="K241"/>
       <x:c r="L241"/>
       <x:c r="M241"/>
       <x:c r="N241"/>
       <x:c r="O241"/>
-      <x:c r="P241" t="str">
-        <x:v>金属-53</x:v>
-      </x:c>
+      <x:c r="P241"/>
       <x:c r="Q241"/>
       <x:c r="R241"/>
       <x:c r="S241"/>
       <x:c r="T241"/>
       <x:c r="U241"/>
-      <x:c r="V241" t="str">
-        <x:v>金属1.3</x:v>
-      </x:c>
+      <x:c r="V241"/>
     </x:row>
     <x:row r="242" ht="21" customHeight="1">
       <x:c r="A242" t="str">
         <x:v>車坂</x:v>
       </x:c>
       <x:c r="B242" t="str">
-        <x:v>病院　薬</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C242" t="n">
         <x:v>243</x:v>
       </x:c>
       <x:c r="D242" t="n">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E242" t="str">
-        <x:v>谷本整形</x:v>
+        <x:v>森辻本店</x:v>
       </x:c>
       <x:c r="F242"/>
       <x:c r="G242" t="str">
-        <x:v>21-0934</x:v>
+        <x:v>21-0505</x:v>
       </x:c>
       <x:c r="H242" t="str">
-        <x:v>H-55</x:v>
+        <x:v>H-56</x:v>
       </x:c>
       <x:c r="I242"/>
-      <x:c r="J242"/>
+      <x:c r="J242" t="str">
+        <x:v>K-8</x:v>
+      </x:c>
       <x:c r="K242"/>
-      <x:c r="L242"/>
+      <x:c r="L242" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M242"/>
       <x:c r="N242"/>
       <x:c r="O242"/>
@@ -11555,35 +11561,29 @@
     </x:row>
     <x:row r="243" ht="21" customHeight="1">
       <x:c r="A243" t="str">
-        <x:v>車坂</x:v>
+        <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B243" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C243" t="n">
         <x:v>244</x:v>
       </x:c>
       <x:c r="D243" t="n">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E243" t="str">
-        <x:v>森辻本店</x:v>
+        <x:v>サックスデザイン</x:v>
       </x:c>
       <x:c r="F243"/>
-      <x:c r="G243" t="str">
-        <x:v>21-0505</x:v>
-      </x:c>
-      <x:c r="H243" t="str">
-        <x:v>H-56</x:v>
-      </x:c>
-      <x:c r="I243"/>
-      <x:c r="J243" t="str">
-        <x:v>K-8</x:v>
-      </x:c>
+      <x:c r="G243"/>
+      <x:c r="H243"/>
+      <x:c r="I243" t="str">
+        <x:v>K-25</x:v>
+      </x:c>
+      <x:c r="J243"/>
       <x:c r="K243"/>
-      <x:c r="L243" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L243"/>
       <x:c r="M243"/>
       <x:c r="N243"/>
       <x:c r="O243"/>
@@ -11606,16 +11606,18 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="D244" t="n">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E244" t="str">
-        <x:v>サックスデザイン</x:v>
+        <x:v>パナソニックテクニカル</x:v>
       </x:c>
       <x:c r="F244"/>
-      <x:c r="G244"/>
+      <x:c r="G244" t="str">
+        <x:v>23-1214</x:v>
+      </x:c>
       <x:c r="H244"/>
       <x:c r="I244" t="str">
-        <x:v>K-25</x:v>
+        <x:v>K-26</x:v>
       </x:c>
       <x:c r="J244"/>
       <x:c r="K244"/>
@@ -11636,24 +11638,22 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B245" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C245" t="n">
         <x:v>246</x:v>
       </x:c>
       <x:c r="D245" t="n">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E245" t="str">
-        <x:v>パナソニックテクニカル</x:v>
+        <x:v>ハイツミヤタ</x:v>
       </x:c>
       <x:c r="F245"/>
-      <x:c r="G245" t="str">
-        <x:v>23-1214</x:v>
-      </x:c>
+      <x:c r="G245"/>
       <x:c r="H245"/>
       <x:c r="I245" t="str">
-        <x:v>K-26</x:v>
+        <x:v>K-27</x:v>
       </x:c>
       <x:c r="J245"/>
       <x:c r="K245"/>
@@ -11674,34 +11674,56 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B246" t="str">
-        <x:v>マンション</x:v>
+        <x:v>コンビニ</x:v>
       </x:c>
       <x:c r="C246" t="n">
         <x:v>247</x:v>
       </x:c>
       <x:c r="D246" t="n">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E246" t="str">
-        <x:v>ハイツミヤタ</x:v>
-      </x:c>
-      <x:c r="F246"/>
-      <x:c r="G246"/>
-      <x:c r="H246"/>
+        <x:v>セブンイレブン緑ヶ丘東町店</x:v>
+      </x:c>
+      <x:c r="F246" t="str">
+        <x:v>計量</x:v>
+      </x:c>
+      <x:c r="G246" t="str">
+        <x:v>24-8677</x:v>
+      </x:c>
+      <x:c r="H246" t="str">
+        <x:v>H-12</x:v>
+      </x:c>
       <x:c r="I246" t="str">
-        <x:v>K-27</x:v>
-      </x:c>
-      <x:c r="J246"/>
-      <x:c r="K246"/>
-      <x:c r="L246"/>
-      <x:c r="M246"/>
-      <x:c r="N246"/>
+        <x:v>K-24</x:v>
+      </x:c>
+      <x:c r="J246" t="str">
+        <x:v>K-7</x:v>
+      </x:c>
+      <x:c r="K246" t="str">
+        <x:v>N-10</x:v>
+      </x:c>
+      <x:c r="L246" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="M246" t="str">
+        <x:v>外-5</x:v>
+      </x:c>
+      <x:c r="N246" t="str">
+        <x:v>段紙(土)-3</x:v>
+      </x:c>
       <x:c r="O246"/>
-      <x:c r="P246"/>
-      <x:c r="Q246"/>
+      <x:c r="P246" t="str">
+        <x:v>金属-14</x:v>
+      </x:c>
+      <x:c r="Q246" t="str">
+        <x:v>段紙-12</x:v>
+      </x:c>
       <x:c r="R246"/>
       <x:c r="S246"/>
-      <x:c r="T246"/>
+      <x:c r="T246" t="str">
+        <x:v>5/31~</x:v>
+      </x:c>
       <x:c r="U246"/>
       <x:c r="V246"/>
     </x:row>
@@ -11710,56 +11732,36 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B247" t="str">
-        <x:v>コンビニ</x:v>
+        <x:v>官公庁</x:v>
       </x:c>
       <x:c r="C247" t="n">
         <x:v>248</x:v>
       </x:c>
       <x:c r="D247" t="n">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E247" t="str">
-        <x:v>セブンイレブン緑ヶ丘東町店</x:v>
-      </x:c>
-      <x:c r="F247" t="str">
-        <x:v>計量</x:v>
-      </x:c>
-      <x:c r="G247" t="str">
-        <x:v>24-8677</x:v>
-      </x:c>
-      <x:c r="H247" t="str">
-        <x:v>H-12</x:v>
-      </x:c>
+        <x:v>上野税務署</x:v>
+      </x:c>
+      <x:c r="F247"/>
+      <x:c r="G247"/>
+      <x:c r="H247"/>
       <x:c r="I247" t="str">
-        <x:v>K-24</x:v>
-      </x:c>
-      <x:c r="J247" t="str">
-        <x:v>K-7</x:v>
-      </x:c>
-      <x:c r="K247" t="str">
-        <x:v>N-10</x:v>
-      </x:c>
+        <x:v>K-23</x:v>
+      </x:c>
+      <x:c r="J247"/>
+      <x:c r="K247"/>
       <x:c r="L247" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="M247" t="str">
-        <x:v>外-5</x:v>
-      </x:c>
-      <x:c r="N247" t="str">
-        <x:v>段紙(土)-3</x:v>
-      </x:c>
+      <x:c r="M247"/>
+      <x:c r="N247"/>
       <x:c r="O247"/>
-      <x:c r="P247" t="str">
-        <x:v>金属-14</x:v>
-      </x:c>
-      <x:c r="Q247" t="str">
-        <x:v>段紙-12</x:v>
-      </x:c>
+      <x:c r="P247"/>
+      <x:c r="Q247"/>
       <x:c r="R247"/>
       <x:c r="S247"/>
-      <x:c r="T247" t="str">
-        <x:v>5/31~</x:v>
-      </x:c>
+      <x:c r="T247"/>
       <x:c r="U247"/>
       <x:c r="V247"/>
     </x:row>
@@ -11768,36 +11770,56 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B248" t="str">
-        <x:v>官公庁</x:v>
+        <x:v>コンビニ</x:v>
       </x:c>
       <x:c r="C248" t="n">
         <x:v>249</x:v>
       </x:c>
       <x:c r="D248" t="n">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E248" t="str">
-        <x:v>上野税務署</x:v>
-      </x:c>
-      <x:c r="F248"/>
-      <x:c r="G248"/>
-      <x:c r="H248"/>
+        <x:v>セブンイレブン緑ヶ丘本町店</x:v>
+      </x:c>
+      <x:c r="F248" t="str">
+        <x:v>計量</x:v>
+      </x:c>
+      <x:c r="G248" t="str">
+        <x:v>24-5113</x:v>
+      </x:c>
+      <x:c r="H248" t="str">
+        <x:v>H-13</x:v>
+      </x:c>
       <x:c r="I248" t="str">
-        <x:v>K-23</x:v>
-      </x:c>
-      <x:c r="J248"/>
-      <x:c r="K248"/>
+        <x:v>K-22</x:v>
+      </x:c>
+      <x:c r="J248" t="str">
+        <x:v>K-6</x:v>
+      </x:c>
+      <x:c r="K248" t="str">
+        <x:v>N-9</x:v>
+      </x:c>
       <x:c r="L248" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="M248"/>
-      <x:c r="N248"/>
+      <x:c r="M248" t="str">
+        <x:v>外-4</x:v>
+      </x:c>
+      <x:c r="N248" t="str">
+        <x:v>段紙(土)-4</x:v>
+      </x:c>
       <x:c r="O248"/>
-      <x:c r="P248"/>
-      <x:c r="Q248"/>
+      <x:c r="P248" t="str">
+        <x:v>金属-15</x:v>
+      </x:c>
+      <x:c r="Q248" t="str">
+        <x:v>段紙-13</x:v>
+      </x:c>
       <x:c r="R248"/>
       <x:c r="S248"/>
-      <x:c r="T248"/>
+      <x:c r="T248" t="str">
+        <x:v>7/28~</x:v>
+      </x:c>
       <x:c r="U248"/>
       <x:c r="V248"/>
     </x:row>
@@ -11806,56 +11828,34 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B249" t="str">
-        <x:v>コンビニ</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C249" t="n">
         <x:v>250</x:v>
       </x:c>
       <x:c r="D249" t="n">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E249" t="str">
-        <x:v>セブンイレブン緑ヶ丘本町店</x:v>
-      </x:c>
-      <x:c r="F249" t="str">
-        <x:v>計量</x:v>
-      </x:c>
-      <x:c r="G249" t="str">
-        <x:v>24-5113</x:v>
-      </x:c>
-      <x:c r="H249" t="str">
-        <x:v>H-13</x:v>
-      </x:c>
-      <x:c r="I249" t="str">
-        <x:v>K-22</x:v>
-      </x:c>
+        <x:v>川口アパート</x:v>
+      </x:c>
+      <x:c r="F249"/>
+      <x:c r="G249"/>
+      <x:c r="H249"/>
+      <x:c r="I249"/>
       <x:c r="J249" t="str">
-        <x:v>K-6</x:v>
-      </x:c>
-      <x:c r="K249" t="str">
-        <x:v>N-9</x:v>
-      </x:c>
-      <x:c r="L249" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="M249" t="str">
-        <x:v>外-4</x:v>
-      </x:c>
-      <x:c r="N249" t="str">
-        <x:v>段紙(土)-4</x:v>
-      </x:c>
+      <x:c r="K249"/>
+      <x:c r="L249"/>
+      <x:c r="M249"/>
+      <x:c r="N249"/>
       <x:c r="O249"/>
-      <x:c r="P249" t="str">
-        <x:v>金属-15</x:v>
-      </x:c>
-      <x:c r="Q249" t="str">
-        <x:v>段紙-13</x:v>
-      </x:c>
+      <x:c r="P249"/>
+      <x:c r="Q249"/>
       <x:c r="R249"/>
       <x:c r="S249"/>
-      <x:c r="T249" t="str">
-        <x:v>7/28~</x:v>
-      </x:c>
+      <x:c r="T249"/>
       <x:c r="U249"/>
       <x:c r="V249"/>
     </x:row>
@@ -11870,24 +11870,28 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="D250" t="n">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E250" t="str">
-        <x:v>川口アパート</x:v>
+        <x:v>エビスマンション</x:v>
       </x:c>
       <x:c r="F250"/>
-      <x:c r="G250"/>
+      <x:c r="G250" t="str">
+        <x:v>21-0832</x:v>
+      </x:c>
       <x:c r="H250"/>
       <x:c r="I250"/>
       <x:c r="J250" t="str">
-        <x:v>M-</x:v>
+        <x:v>K-5</x:v>
       </x:c>
       <x:c r="K250"/>
       <x:c r="L250"/>
       <x:c r="M250"/>
       <x:c r="N250"/>
       <x:c r="O250"/>
-      <x:c r="P250"/>
+      <x:c r="P250" t="str">
+        <x:v>金属-17</x:v>
+      </x:c>
       <x:c r="Q250"/>
       <x:c r="R250"/>
       <x:c r="S250"/>
@@ -11906,10 +11910,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="D251" t="n">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="E251" t="str">
-        <x:v>エビスマンション</x:v>
+        <x:v>エビスコーポ</x:v>
       </x:c>
       <x:c r="F251"/>
       <x:c r="G251" t="str">
@@ -11918,7 +11922,7 @@
       <x:c r="H251"/>
       <x:c r="I251"/>
       <x:c r="J251" t="str">
-        <x:v>K-5</x:v>
+        <x:v>K-4</x:v>
       </x:c>
       <x:c r="K251"/>
       <x:c r="L251"/>
@@ -11926,7 +11930,7 @@
       <x:c r="N251"/>
       <x:c r="O251"/>
       <x:c r="P251" t="str">
-        <x:v>金属-17</x:v>
+        <x:v>金属-18</x:v>
       </x:c>
       <x:c r="Q251"/>
       <x:c r="R251"/>
@@ -11946,30 +11950,34 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="D252" t="n">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E252" t="str">
-        <x:v>エビスコーポ</x:v>
+        <x:v>エバーグリーン</x:v>
       </x:c>
       <x:c r="F252"/>
       <x:c r="G252" t="str">
-        <x:v>21-0832</x:v>
+        <x:v>63-5430</x:v>
       </x:c>
       <x:c r="H252"/>
-      <x:c r="I252"/>
-      <x:c r="J252" t="str">
-        <x:v>K-4</x:v>
-      </x:c>
+      <x:c r="I252" t="str">
+        <x:v>K-21</x:v>
+      </x:c>
+      <x:c r="J252"/>
       <x:c r="K252"/>
-      <x:c r="L252"/>
+      <x:c r="L252" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M252"/>
       <x:c r="N252"/>
       <x:c r="O252"/>
       <x:c r="P252" t="str">
-        <x:v>金属-18</x:v>
+        <x:v>金属-16</x:v>
       </x:c>
       <x:c r="Q252"/>
-      <x:c r="R252"/>
+      <x:c r="R252" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S252"/>
       <x:c r="T252"/>
       <x:c r="U252"/>
@@ -11986,34 +11994,26 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="D253" t="n">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E253" t="str">
-        <x:v>エバーグリーン</x:v>
+        <x:v>クラリティ雅</x:v>
       </x:c>
       <x:c r="F253"/>
-      <x:c r="G253" t="str">
-        <x:v>63-5430</x:v>
-      </x:c>
+      <x:c r="G253"/>
       <x:c r="H253"/>
-      <x:c r="I253" t="str">
-        <x:v>K-21</x:v>
-      </x:c>
+      <x:c r="I253"/>
       <x:c r="J253"/>
-      <x:c r="K253"/>
-      <x:c r="L253" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="K253" t="str">
+        <x:v>N-11</x:v>
+      </x:c>
+      <x:c r="L253"/>
       <x:c r="M253"/>
       <x:c r="N253"/>
       <x:c r="O253"/>
-      <x:c r="P253" t="str">
-        <x:v>金属-16</x:v>
-      </x:c>
+      <x:c r="P253"/>
       <x:c r="Q253"/>
-      <x:c r="R253" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R253"/>
       <x:c r="S253"/>
       <x:c r="T253"/>
       <x:c r="U253"/>
@@ -12024,26 +12024,26 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B254" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C254" t="n">
         <x:v>255</x:v>
       </x:c>
       <x:c r="D254" t="n">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E254" t="str">
-        <x:v>クラリティ雅</x:v>
+        <x:v>SHOICHI</x:v>
       </x:c>
       <x:c r="F254"/>
       <x:c r="G254"/>
       <x:c r="H254"/>
       <x:c r="I254"/>
       <x:c r="J254"/>
-      <x:c r="K254" t="str">
-        <x:v>N-11</x:v>
-      </x:c>
-      <x:c r="L254"/>
+      <x:c r="K254"/>
+      <x:c r="L254" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M254"/>
       <x:c r="N254"/>
       <x:c r="O254"/>
@@ -12066,13 +12066,15 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="D255" t="n">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E255" t="str">
-        <x:v>SHOICHI</x:v>
+        <x:v>吉岡税理</x:v>
       </x:c>
       <x:c r="F255"/>
-      <x:c r="G255"/>
+      <x:c r="G255" t="str">
+        <x:v>21-1747</x:v>
+      </x:c>
       <x:c r="H255"/>
       <x:c r="I255"/>
       <x:c r="J255"/>
@@ -12096,32 +12098,32 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B256" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C256" t="n">
         <x:v>257</x:v>
       </x:c>
       <x:c r="D256" t="n">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E256" t="str">
-        <x:v>吉岡税理</x:v>
+        <x:v>グリーンヒル福山</x:v>
       </x:c>
       <x:c r="F256"/>
-      <x:c r="G256" t="str">
-        <x:v>21-1747</x:v>
-      </x:c>
+      <x:c r="G256"/>
       <x:c r="H256"/>
       <x:c r="I256"/>
-      <x:c r="J256"/>
+      <x:c r="J256" t="str">
+        <x:v>K-9</x:v>
+      </x:c>
       <x:c r="K256"/>
-      <x:c r="L256" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L256"/>
       <x:c r="M256"/>
       <x:c r="N256"/>
       <x:c r="O256"/>
-      <x:c r="P256"/>
+      <x:c r="P256" t="str">
+        <x:v>金属-13</x:v>
+      </x:c>
       <x:c r="Q256"/>
       <x:c r="R256"/>
       <x:c r="S256"/>
@@ -12134,22 +12136,24 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B257" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C257" t="n">
         <x:v>258</x:v>
       </x:c>
       <x:c r="D257" t="n">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E257" t="str">
-        <x:v>michi</x:v>
+        <x:v>メゾンベルト桑原工業（株）</x:v>
       </x:c>
       <x:c r="F257"/>
       <x:c r="G257"/>
       <x:c r="H257"/>
       <x:c r="I257"/>
-      <x:c r="J257"/>
+      <x:c r="J257" t="str">
+        <x:v>K-10</x:v>
+      </x:c>
       <x:c r="K257"/>
       <x:c r="L257"/>
       <x:c r="M257"/>
@@ -12161,77 +12165,81 @@
       <x:c r="S257"/>
       <x:c r="T257"/>
       <x:c r="U257"/>
-      <x:c r="V257"/>
+      <x:c r="V257" t="str">
+        <x:v>1.3水曜日</x:v>
+      </x:c>
     </x:row>
     <x:row r="258" ht="21" customHeight="1">
       <x:c r="A258" t="str">
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B258" t="str">
-        <x:v>ヘアカット</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C258" t="n">
         <x:v>259</x:v>
       </x:c>
       <x:c r="D258" t="n">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E258" t="str">
-        <x:v>ソレイユ緑ヶ丘店</x:v>
+        <x:v>いえちか　どっとこむ</x:v>
       </x:c>
       <x:c r="F258"/>
-      <x:c r="G258" t="str">
-        <x:v>21-3754</x:v>
-      </x:c>
+      <x:c r="G258"/>
       <x:c r="H258"/>
       <x:c r="I258"/>
-      <x:c r="J258"/>
+      <x:c r="J258" t="str">
+        <x:v>K-11</x:v>
+      </x:c>
       <x:c r="K258"/>
-      <x:c r="L258" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L258"/>
       <x:c r="M258"/>
       <x:c r="N258"/>
       <x:c r="O258"/>
-      <x:c r="P258"/>
+      <x:c r="P258" t="str">
+        <x:v>金属-12</x:v>
+      </x:c>
       <x:c r="Q258"/>
       <x:c r="R258"/>
       <x:c r="S258"/>
       <x:c r="T258"/>
       <x:c r="U258"/>
-      <x:c r="V258"/>
+      <x:c r="V258" t="str">
+        <x:v>1.3水曜日</x:v>
+      </x:c>
     </x:row>
     <x:row r="259" ht="21" customHeight="1">
       <x:c r="A259" t="str">
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B259" t="str">
-        <x:v>マンション</x:v>
+        <x:v>銀行</x:v>
       </x:c>
       <x:c r="C259" t="n">
         <x:v>260</x:v>
       </x:c>
       <x:c r="D259" t="n">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E259" t="str">
-        <x:v>グリーンヒル福山</x:v>
+        <x:v>百五銀行　緑が丘支店</x:v>
       </x:c>
       <x:c r="F259"/>
-      <x:c r="G259"/>
+      <x:c r="G259" t="str">
+        <x:v>24-4105</x:v>
+      </x:c>
       <x:c r="H259"/>
       <x:c r="I259"/>
-      <x:c r="J259" t="str">
-        <x:v>K-9</x:v>
-      </x:c>
+      <x:c r="J259"/>
       <x:c r="K259"/>
-      <x:c r="L259"/>
+      <x:c r="L259" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M259"/>
       <x:c r="N259"/>
       <x:c r="O259"/>
-      <x:c r="P259" t="str">
-        <x:v>金属-13</x:v>
-      </x:c>
+      <x:c r="P259"/>
       <x:c r="Q259"/>
       <x:c r="R259"/>
       <x:c r="S259"/>
@@ -12250,19 +12258,21 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="D260" t="n">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E260" t="str">
-        <x:v>メゾンベルト桑原工業（株）</x:v>
+        <x:v>朝日パンション</x:v>
       </x:c>
       <x:c r="F260"/>
       <x:c r="G260"/>
-      <x:c r="H260"/>
+      <x:c r="H260" t="str">
+        <x:v>H-11</x:v>
+      </x:c>
       <x:c r="I260"/>
-      <x:c r="J260" t="str">
-        <x:v>K-10</x:v>
-      </x:c>
-      <x:c r="K260"/>
+      <x:c r="J260"/>
+      <x:c r="K260" t="str">
+        <x:v>N-7</x:v>
+      </x:c>
       <x:c r="L260"/>
       <x:c r="M260"/>
       <x:c r="N260"/>
@@ -12271,11 +12281,11 @@
       <x:c r="Q260"/>
       <x:c r="R260"/>
       <x:c r="S260"/>
-      <x:c r="T260"/>
+      <x:c r="T260" t="str">
+        <x:v>不燃 第2第4</x:v>
+      </x:c>
       <x:c r="U260"/>
-      <x:c r="V260" t="str">
-        <x:v>1.3水曜日</x:v>
-      </x:c>
+      <x:c r="V260"/>
     </x:row>
     <x:row r="261" ht="21" customHeight="1">
       <x:c r="A261" t="str">
@@ -12288,58 +12298,58 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="D261" t="n">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E261" t="str">
-        <x:v>いえちか　どっとこむ</x:v>
+        <x:v>太平荘</x:v>
       </x:c>
       <x:c r="F261"/>
       <x:c r="G261"/>
       <x:c r="H261"/>
-      <x:c r="I261"/>
-      <x:c r="J261" t="str">
-        <x:v>K-11</x:v>
-      </x:c>
+      <x:c r="I261" t="str">
+        <x:v>K-28</x:v>
+      </x:c>
+      <x:c r="J261"/>
       <x:c r="K261"/>
       <x:c r="L261"/>
       <x:c r="M261"/>
       <x:c r="N261"/>
       <x:c r="O261"/>
-      <x:c r="P261" t="str">
-        <x:v>金属-12</x:v>
-      </x:c>
+      <x:c r="P261"/>
       <x:c r="Q261"/>
       <x:c r="R261"/>
       <x:c r="S261"/>
       <x:c r="T261"/>
       <x:c r="U261"/>
-      <x:c r="V261" t="str">
-        <x:v>1.3水曜日</x:v>
-      </x:c>
+      <x:c r="V261"/>
     </x:row>
     <x:row r="262" ht="21" customHeight="1">
       <x:c r="A262" t="str">
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B262" t="str">
-        <x:v>銀行</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C262" t="n">
         <x:v>263</x:v>
       </x:c>
       <x:c r="D262" t="n">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E262" t="str">
-        <x:v>百五銀行　緑が丘支店</x:v>
+        <x:v>安永　本社</x:v>
       </x:c>
       <x:c r="F262"/>
       <x:c r="G262" t="str">
-        <x:v>24-4105</x:v>
-      </x:c>
-      <x:c r="H262"/>
+        <x:v>24-2111</x:v>
+      </x:c>
+      <x:c r="H262" t="str">
+        <x:v>H-10</x:v>
+      </x:c>
       <x:c r="I262"/>
-      <x:c r="J262"/>
+      <x:c r="J262" t="str">
+        <x:v>K-12</x:v>
+      </x:c>
       <x:c r="K262"/>
       <x:c r="L262" t="str">
         <x:v>M-</x:v>
@@ -12347,9 +12357,13 @@
       <x:c r="M262"/>
       <x:c r="N262"/>
       <x:c r="O262"/>
-      <x:c r="P262"/>
+      <x:c r="P262" t="str">
+        <x:v>金属-11</x:v>
+      </x:c>
       <x:c r="Q262"/>
-      <x:c r="R262"/>
+      <x:c r="R262" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S262"/>
       <x:c r="T262"/>
       <x:c r="U262"/>
@@ -12360,27 +12374,25 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B263" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C263" t="n">
         <x:v>264</x:v>
       </x:c>
       <x:c r="D263" t="n">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E263" t="str">
-        <x:v>朝日パンション</x:v>
+        <x:v>安永　社員寮</x:v>
       </x:c>
       <x:c r="F263"/>
       <x:c r="G263"/>
-      <x:c r="H263" t="str">
-        <x:v>H-11</x:v>
-      </x:c>
+      <x:c r="H263"/>
       <x:c r="I263"/>
-      <x:c r="J263"/>
-      <x:c r="K263" t="str">
-        <x:v>N-7</x:v>
-      </x:c>
+      <x:c r="J263" t="str">
+        <x:v>K-13</x:v>
+      </x:c>
+      <x:c r="K263"/>
       <x:c r="L263"/>
       <x:c r="M263"/>
       <x:c r="N263"/>
@@ -12390,7 +12402,7 @@
       <x:c r="R263"/>
       <x:c r="S263"/>
       <x:c r="T263" t="str">
-        <x:v>不燃 第2第4</x:v>
+        <x:v>可燃のみ収集</x:v>
       </x:c>
       <x:c r="U263"/>
       <x:c r="V263"/>
@@ -12400,32 +12412,42 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B264" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C264" t="n">
         <x:v>265</x:v>
       </x:c>
       <x:c r="D264" t="n">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E264" t="str">
-        <x:v>太平荘</x:v>
+        <x:v>安永　西明寺</x:v>
       </x:c>
       <x:c r="F264"/>
-      <x:c r="G264"/>
-      <x:c r="H264"/>
-      <x:c r="I264" t="str">
-        <x:v>K-28</x:v>
-      </x:c>
-      <x:c r="J264"/>
+      <x:c r="G264" t="str">
+        <x:v>24-2155</x:v>
+      </x:c>
+      <x:c r="H264" t="str">
+        <x:v>H-8</x:v>
+      </x:c>
+      <x:c r="I264"/>
+      <x:c r="J264" t="str">
+        <x:v>K-18</x:v>
+      </x:c>
       <x:c r="K264"/>
-      <x:c r="L264"/>
+      <x:c r="L264" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M264"/>
       <x:c r="N264"/>
       <x:c r="O264"/>
-      <x:c r="P264"/>
+      <x:c r="P264" t="str">
+        <x:v>金属-8</x:v>
+      </x:c>
       <x:c r="Q264"/>
-      <x:c r="R264"/>
+      <x:c r="R264" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S264"/>
       <x:c r="T264"/>
       <x:c r="U264"/>
@@ -12442,21 +12464,21 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="D265" t="n">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E265" t="str">
-        <x:v>安永　本社</x:v>
+        <x:v>安永　運輸</x:v>
       </x:c>
       <x:c r="F265"/>
       <x:c r="G265" t="str">
-        <x:v>24-2111</x:v>
+        <x:v>21-2913</x:v>
       </x:c>
       <x:c r="H265" t="str">
-        <x:v>H-10</x:v>
+        <x:v>H-7</x:v>
       </x:c>
       <x:c r="I265"/>
       <x:c r="J265" t="str">
-        <x:v>K-12</x:v>
+        <x:v>K-17</x:v>
       </x:c>
       <x:c r="K265"/>
       <x:c r="L265" t="str">
@@ -12465,13 +12487,9 @@
       <x:c r="M265"/>
       <x:c r="N265"/>
       <x:c r="O265"/>
-      <x:c r="P265" t="str">
-        <x:v>金属-11</x:v>
-      </x:c>
+      <x:c r="P265"/>
       <x:c r="Q265"/>
-      <x:c r="R265" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R265"/>
       <x:c r="S265"/>
       <x:c r="T265"/>
       <x:c r="U265"/>
@@ -12488,30 +12506,34 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="D266" t="n">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E266" t="str">
-        <x:v>安永　社員寮</x:v>
+        <x:v>安永　キャスティング</x:v>
       </x:c>
       <x:c r="F266"/>
       <x:c r="G266"/>
-      <x:c r="H266"/>
+      <x:c r="H266" t="str">
+        <x:v>H-9</x:v>
+      </x:c>
       <x:c r="I266"/>
       <x:c r="J266" t="str">
-        <x:v>K-13</x:v>
+        <x:v>K-14</x:v>
       </x:c>
       <x:c r="K266"/>
-      <x:c r="L266"/>
+      <x:c r="L266" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M266"/>
       <x:c r="N266"/>
       <x:c r="O266"/>
       <x:c r="P266"/>
       <x:c r="Q266"/>
-      <x:c r="R266"/>
+      <x:c r="R266" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S266"/>
-      <x:c r="T266" t="str">
-        <x:v>可燃のみ収集</x:v>
-      </x:c>
+      <x:c r="T266"/>
       <x:c r="U266"/>
       <x:c r="V266"/>
     </x:row>
@@ -12520,28 +12542,24 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B267" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>介護</x:v>
       </x:c>
       <x:c r="C267" t="n">
         <x:v>268</x:v>
       </x:c>
       <x:c r="D267" t="n">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E267" t="str">
-        <x:v>安永　西明寺</x:v>
+        <x:v>ソーシャルインクルー株式会社　SIH伊賀西明寺</x:v>
       </x:c>
       <x:c r="F267"/>
-      <x:c r="G267" t="str">
-        <x:v>24-2155</x:v>
-      </x:c>
-      <x:c r="H267" t="str">
-        <x:v>H-8</x:v>
-      </x:c>
-      <x:c r="I267"/>
-      <x:c r="J267" t="str">
-        <x:v>K-18</x:v>
-      </x:c>
+      <x:c r="G267"/>
+      <x:c r="H267"/>
+      <x:c r="I267" t="str">
+        <x:v>K-33</x:v>
+      </x:c>
+      <x:c r="J267"/>
       <x:c r="K267"/>
       <x:c r="L267" t="str">
         <x:v>M-</x:v>
@@ -12549,13 +12567,9 @@
       <x:c r="M267"/>
       <x:c r="N267"/>
       <x:c r="O267"/>
-      <x:c r="P267" t="str">
-        <x:v>金属-8</x:v>
-      </x:c>
+      <x:c r="P267"/>
       <x:c r="Q267"/>
-      <x:c r="R267" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R267"/>
       <x:c r="S267"/>
       <x:c r="T267"/>
       <x:c r="U267"/>
@@ -12566,28 +12580,24 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B268" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>車 ガソリン</x:v>
       </x:c>
       <x:c r="C268" t="n">
         <x:v>269</x:v>
       </x:c>
       <x:c r="D268" t="n">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E268" t="str">
-        <x:v>安永　運輸</x:v>
+        <x:v>ロジスネクスト中部株式会社</x:v>
       </x:c>
       <x:c r="F268"/>
       <x:c r="G268" t="str">
-        <x:v>21-2913</x:v>
-      </x:c>
-      <x:c r="H268" t="str">
-        <x:v>H-7</x:v>
-      </x:c>
+        <x:v>24-6464</x:v>
+      </x:c>
+      <x:c r="H268"/>
       <x:c r="I268"/>
-      <x:c r="J268" t="str">
-        <x:v>K-17</x:v>
-      </x:c>
+      <x:c r="J268"/>
       <x:c r="K268"/>
       <x:c r="L268" t="str">
         <x:v>M-</x:v>
@@ -12599,7 +12609,9 @@
       <x:c r="Q268"/>
       <x:c r="R268"/>
       <x:c r="S268"/>
-      <x:c r="T268"/>
+      <x:c r="T268" t="str">
+        <x:v>旧ニチユ</x:v>
+      </x:c>
       <x:c r="U268"/>
       <x:c r="V268"/>
     </x:row>
@@ -12614,20 +12626,18 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="D269" t="n">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E269" t="str">
-        <x:v>安永　キャスティング</x:v>
+        <x:v>富士産業株式会社</x:v>
       </x:c>
       <x:c r="F269"/>
-      <x:c r="G269"/>
-      <x:c r="H269" t="str">
-        <x:v>H-9</x:v>
-      </x:c>
+      <x:c r="G269" t="str">
+        <x:v>26-1300</x:v>
+      </x:c>
+      <x:c r="H269"/>
       <x:c r="I269"/>
-      <x:c r="J269" t="str">
-        <x:v>K-14</x:v>
-      </x:c>
+      <x:c r="J269"/>
       <x:c r="K269"/>
       <x:c r="L269" t="str">
         <x:v>M-</x:v>
@@ -12637,9 +12647,7 @@
       <x:c r="O269"/>
       <x:c r="P269"/>
       <x:c r="Q269"/>
-      <x:c r="R269" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R269"/>
       <x:c r="S269"/>
       <x:c r="T269"/>
       <x:c r="U269"/>
@@ -12650,28 +12658,24 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B270" t="str">
-        <x:v>介護</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C270" t="n">
         <x:v>271</x:v>
       </x:c>
       <x:c r="D270" t="n">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E270" t="str">
-        <x:v>ソーシャルインクルー株式会社　SIH伊賀西明寺</x:v>
+        <x:v>フィオーレA.B</x:v>
       </x:c>
       <x:c r="F270"/>
       <x:c r="G270"/>
       <x:c r="H270"/>
-      <x:c r="I270" t="str">
-        <x:v>K-33</x:v>
-      </x:c>
+      <x:c r="I270"/>
       <x:c r="J270"/>
       <x:c r="K270"/>
-      <x:c r="L270" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L270"/>
       <x:c r="M270"/>
       <x:c r="N270"/>
       <x:c r="O270"/>
@@ -12688,38 +12692,52 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B271" t="str">
-        <x:v>車 ガソリン</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C271" t="n">
         <x:v>272</x:v>
       </x:c>
       <x:c r="D271" t="n">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E271" t="str">
-        <x:v>ロジスネクスト中部株式会社</x:v>
+        <x:v>サンピア</x:v>
       </x:c>
       <x:c r="F271"/>
       <x:c r="G271" t="str">
-        <x:v>24-6464</x:v>
-      </x:c>
-      <x:c r="H271"/>
-      <x:c r="I271"/>
-      <x:c r="J271"/>
-      <x:c r="K271"/>
+        <x:v>24-7000</x:v>
+      </x:c>
+      <x:c r="H271" t="str">
+        <x:v>H-6</x:v>
+      </x:c>
+      <x:c r="I271" t="str">
+        <x:v>K-36</x:v>
+      </x:c>
+      <x:c r="J271" t="str">
+        <x:v>K-15</x:v>
+      </x:c>
+      <x:c r="K271" t="str">
+        <x:v>N-6</x:v>
+      </x:c>
       <x:c r="L271" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="M271"/>
-      <x:c r="N271"/>
+      <x:c r="M271" t="str">
+        <x:v>外-2</x:v>
+      </x:c>
+      <x:c r="N271" t="str">
+        <x:v>段紙(土)-5</x:v>
+      </x:c>
       <x:c r="O271"/>
-      <x:c r="P271"/>
+      <x:c r="P271" t="str">
+        <x:v>金属-7</x:v>
+      </x:c>
       <x:c r="Q271"/>
-      <x:c r="R271"/>
+      <x:c r="R271" t="str">
+        <x:v>ガラ-</x:v>
+      </x:c>
       <x:c r="S271"/>
-      <x:c r="T271" t="str">
-        <x:v>旧ニチユ</x:v>
-      </x:c>
+      <x:c r="T271"/>
       <x:c r="U271"/>
       <x:c r="V271"/>
     </x:row>
@@ -12728,23 +12746,25 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B272" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>介護</x:v>
       </x:c>
       <x:c r="C272" t="n">
         <x:v>273</x:v>
       </x:c>
       <x:c r="D272" t="n">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E272" t="str">
-        <x:v>富士産業株式会社</x:v>
+        <x:v>よい子のお家伊賀</x:v>
       </x:c>
       <x:c r="F272"/>
       <x:c r="G272" t="str">
-        <x:v>26-1300</x:v>
+        <x:v>48-7771</x:v>
       </x:c>
       <x:c r="H272"/>
-      <x:c r="I272"/>
+      <x:c r="I272" t="str">
+        <x:v>K-13</x:v>
+      </x:c>
       <x:c r="J272"/>
       <x:c r="K272"/>
       <x:c r="L272" t="str">
@@ -12757,33 +12777,43 @@
       <x:c r="Q272"/>
       <x:c r="R272"/>
       <x:c r="S272"/>
-      <x:c r="T272"/>
+      <x:c r="T272" t="str">
+        <x:v>090-6802-4355宇佐美</x:v>
+      </x:c>
       <x:c r="U272"/>
-      <x:c r="V272"/>
+      <x:c r="V272" t="str">
+        <x:v>1時～</x:v>
+      </x:c>
     </x:row>
     <x:row r="273" ht="21" customHeight="1">
       <x:c r="A273" t="str">
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B273" t="str">
-        <x:v>マンション</x:v>
+        <x:v>ヘアカット</x:v>
       </x:c>
       <x:c r="C273" t="n">
         <x:v>274</x:v>
       </x:c>
       <x:c r="D273" t="n">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E273" t="str">
-        <x:v>フィオーレA.B</x:v>
+        <x:v>Heathpool</x:v>
       </x:c>
       <x:c r="F273"/>
-      <x:c r="G273"/>
+      <x:c r="G273" t="str">
+        <x:v>51-4677</x:v>
+      </x:c>
       <x:c r="H273"/>
-      <x:c r="I273"/>
+      <x:c r="I273" t="str">
+        <x:v>K-29</x:v>
+      </x:c>
       <x:c r="J273"/>
       <x:c r="K273"/>
-      <x:c r="L273"/>
+      <x:c r="L273" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M273"/>
       <x:c r="N273"/>
       <x:c r="O273"/>
@@ -12800,50 +12830,32 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B274" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>個人</x:v>
       </x:c>
       <x:c r="C274" t="n">
         <x:v>275</x:v>
       </x:c>
       <x:c r="D274" t="n">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E274" t="str">
-        <x:v>サンピア</x:v>
+        <x:v>松本貢次郎</x:v>
       </x:c>
       <x:c r="F274"/>
-      <x:c r="G274" t="str">
-        <x:v>24-7000</x:v>
-      </x:c>
-      <x:c r="H274" t="str">
-        <x:v>H-6</x:v>
-      </x:c>
-      <x:c r="I274" t="str">
-        <x:v>K-36</x:v>
-      </x:c>
-      <x:c r="J274" t="str">
-        <x:v>K-15</x:v>
-      </x:c>
+      <x:c r="G274"/>
+      <x:c r="H274"/>
+      <x:c r="I274"/>
+      <x:c r="J274"/>
       <x:c r="K274" t="str">
-        <x:v>N-6</x:v>
-      </x:c>
-      <x:c r="L274" t="str">
-        <x:v>M-</x:v>
-      </x:c>
-      <x:c r="M274" t="str">
-        <x:v>外-2</x:v>
-      </x:c>
-      <x:c r="N274" t="str">
-        <x:v>段紙(土)-5</x:v>
-      </x:c>
+        <x:v>N-8</x:v>
+      </x:c>
+      <x:c r="L274"/>
+      <x:c r="M274"/>
+      <x:c r="N274"/>
       <x:c r="O274"/>
-      <x:c r="P274" t="str">
-        <x:v>金属-7</x:v>
-      </x:c>
+      <x:c r="P274"/>
       <x:c r="Q274"/>
-      <x:c r="R274" t="str">
-        <x:v>ガラ-</x:v>
-      </x:c>
+      <x:c r="R274"/>
       <x:c r="S274"/>
       <x:c r="T274"/>
       <x:c r="U274"/>
@@ -12854,24 +12866,24 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B275" t="str">
-        <x:v>介護</x:v>
+        <x:v>官公庁</x:v>
       </x:c>
       <x:c r="C275" t="n">
         <x:v>276</x:v>
       </x:c>
       <x:c r="D275" t="n">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E275" t="str">
-        <x:v>よい子のお家伊賀</x:v>
+        <x:v>白鳳高校</x:v>
       </x:c>
       <x:c r="F275"/>
       <x:c r="G275" t="str">
-        <x:v>48-7771</x:v>
+        <x:v>21-2110</x:v>
       </x:c>
       <x:c r="H275"/>
       <x:c r="I275" t="str">
-        <x:v>K-13</x:v>
+        <x:v>K-30</x:v>
       </x:c>
       <x:c r="J275"/>
       <x:c r="K275"/>
@@ -12881,16 +12893,16 @@
       <x:c r="M275"/>
       <x:c r="N275"/>
       <x:c r="O275"/>
-      <x:c r="P275"/>
+      <x:c r="P275" t="str">
+        <x:v>金属-10</x:v>
+      </x:c>
       <x:c r="Q275"/>
       <x:c r="R275"/>
       <x:c r="S275"/>
-      <x:c r="T275" t="str">
-        <x:v>090-6802-4355宇佐美</x:v>
-      </x:c>
+      <x:c r="T275"/>
       <x:c r="U275"/>
       <x:c r="V275" t="str">
-        <x:v>1時～</x:v>
+        <x:v>金属1.3.5</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="21" customHeight="1">
@@ -12898,30 +12910,28 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B276" t="str">
-        <x:v>ヘアカット</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C276" t="n">
         <x:v>277</x:v>
       </x:c>
       <x:c r="D276" t="n">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E276" t="str">
-        <x:v>Heathpool</x:v>
+        <x:v>城陽ネジ</x:v>
       </x:c>
       <x:c r="F276"/>
       <x:c r="G276" t="str">
-        <x:v>51-4677</x:v>
+        <x:v>23-1351</x:v>
       </x:c>
       <x:c r="H276"/>
-      <x:c r="I276" t="str">
-        <x:v>K-29</x:v>
-      </x:c>
-      <x:c r="J276"/>
+      <x:c r="I276"/>
+      <x:c r="J276" t="str">
+        <x:v>K-16</x:v>
+      </x:c>
       <x:c r="K276"/>
-      <x:c r="L276" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L276"/>
       <x:c r="M276"/>
       <x:c r="N276"/>
       <x:c r="O276"/>
@@ -12938,26 +12948,26 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B277" t="str">
-        <x:v>個人</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C277" t="n">
         <x:v>278</x:v>
       </x:c>
       <x:c r="D277" t="n">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E277" t="str">
-        <x:v>松本貢次郎</x:v>
+        <x:v>ラグランジュⅠ.Ⅱ</x:v>
       </x:c>
       <x:c r="F277"/>
       <x:c r="G277"/>
       <x:c r="H277"/>
       <x:c r="I277"/>
       <x:c r="J277"/>
-      <x:c r="K277" t="str">
-        <x:v>N-8</x:v>
-      </x:c>
-      <x:c r="L277"/>
+      <x:c r="K277"/>
+      <x:c r="L277" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M277"/>
       <x:c r="N277"/>
       <x:c r="O277"/>
@@ -12974,25 +12984,23 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B278" t="str">
-        <x:v>官公庁</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C278" t="n">
         <x:v>279</x:v>
       </x:c>
       <x:c r="D278" t="n">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E278" t="str">
-        <x:v>白鳳高校</x:v>
+        <x:v>吉川　コーポプレジール</x:v>
       </x:c>
       <x:c r="F278"/>
       <x:c r="G278" t="str">
-        <x:v>21-2110</x:v>
+        <x:v>24-3766</x:v>
       </x:c>
       <x:c r="H278"/>
-      <x:c r="I278" t="str">
-        <x:v>K-30</x:v>
-      </x:c>
+      <x:c r="I278"/>
       <x:c r="J278"/>
       <x:c r="K278"/>
       <x:c r="L278" t="str">
@@ -13001,49 +13009,49 @@
       <x:c r="M278"/>
       <x:c r="N278"/>
       <x:c r="O278"/>
-      <x:c r="P278" t="str">
-        <x:v>金属-10</x:v>
-      </x:c>
+      <x:c r="P278"/>
       <x:c r="Q278"/>
       <x:c r="R278"/>
       <x:c r="S278"/>
       <x:c r="T278"/>
       <x:c r="U278"/>
-      <x:c r="V278" t="str">
-        <x:v>金属1.3.5</x:v>
-      </x:c>
+      <x:c r="V278"/>
     </x:row>
     <x:row r="279" ht="21" customHeight="1">
       <x:c r="A279" t="str">
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B279" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C279" t="n">
         <x:v>280</x:v>
       </x:c>
       <x:c r="D279" t="n">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E279" t="str">
-        <x:v>城陽ネジ</x:v>
+        <x:v>吉川　コンフォート上野</x:v>
       </x:c>
       <x:c r="F279"/>
       <x:c r="G279" t="str">
-        <x:v>23-1351</x:v>
+        <x:v>24-3766</x:v>
       </x:c>
       <x:c r="H279"/>
-      <x:c r="I279"/>
-      <x:c r="J279" t="str">
-        <x:v>K-16</x:v>
-      </x:c>
+      <x:c r="I279" t="str">
+        <x:v>K-32</x:v>
+      </x:c>
+      <x:c r="J279"/>
       <x:c r="K279"/>
-      <x:c r="L279"/>
+      <x:c r="L279" t="str">
+        <x:v>M-</x:v>
+      </x:c>
       <x:c r="M279"/>
       <x:c r="N279"/>
       <x:c r="O279"/>
-      <x:c r="P279"/>
+      <x:c r="P279" t="str">
+        <x:v>金属-9</x:v>
+      </x:c>
       <x:c r="Q279"/>
       <x:c r="R279"/>
       <x:c r="S279"/>
@@ -13062,13 +13070,15 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="D280" t="n">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E280" t="str">
-        <x:v>ラグランジュⅠ.Ⅱ</x:v>
+        <x:v>吉川　ロジュメントAB</x:v>
       </x:c>
       <x:c r="F280"/>
-      <x:c r="G280"/>
+      <x:c r="G280" t="str">
+        <x:v>24-3766</x:v>
+      </x:c>
       <x:c r="H280"/>
       <x:c r="I280"/>
       <x:c r="J280"/>
@@ -13098,14 +13108,14 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="D281" t="n">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E281" t="str">
-        <x:v>吉川　コーポプレジール</x:v>
+        <x:v>幸福ハイツ</x:v>
       </x:c>
       <x:c r="F281"/>
       <x:c r="G281" t="str">
-        <x:v>24-3766</x:v>
+        <x:v>21-1160</x:v>
       </x:c>
       <x:c r="H281"/>
       <x:c r="I281"/>
@@ -13130,36 +13140,32 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B282" t="str">
-        <x:v>マンション</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C282" t="n">
         <x:v>283</x:v>
       </x:c>
       <x:c r="D282" t="n">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E282" t="str">
-        <x:v>吉川　コンフォート上野</x:v>
+        <x:v>雅九</x:v>
       </x:c>
       <x:c r="F282"/>
-      <x:c r="G282" t="str">
-        <x:v>24-3766</x:v>
-      </x:c>
+      <x:c r="G282"/>
       <x:c r="H282"/>
-      <x:c r="I282" t="str">
-        <x:v>K-32</x:v>
-      </x:c>
-      <x:c r="J282"/>
+      <x:c r="I282"/>
+      <x:c r="J282" t="str">
+        <x:v>K-19</x:v>
+      </x:c>
       <x:c r="K282"/>
-      <x:c r="L282" t="str">
-        <x:v>M-</x:v>
-      </x:c>
-      <x:c r="M282"/>
+      <x:c r="L282"/>
+      <x:c r="M282" t="str">
+        <x:v>外-3</x:v>
+      </x:c>
       <x:c r="N282"/>
       <x:c r="O282"/>
-      <x:c r="P282" t="str">
-        <x:v>金属-9</x:v>
-      </x:c>
+      <x:c r="P282"/>
       <x:c r="Q282"/>
       <x:c r="R282"/>
       <x:c r="S282"/>
@@ -13172,28 +13178,28 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B283" t="str">
-        <x:v>マンション</x:v>
+        <x:v>官公庁</x:v>
       </x:c>
       <x:c r="C283" t="n">
         <x:v>284</x:v>
       </x:c>
       <x:c r="D283" t="n">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E283" t="str">
-        <x:v>吉川　ロジュメントAB</x:v>
+        <x:v>旧農業高校</x:v>
       </x:c>
       <x:c r="F283"/>
       <x:c r="G283" t="str">
-        <x:v>24-3766</x:v>
+        <x:v>24-0123</x:v>
       </x:c>
       <x:c r="H283"/>
-      <x:c r="I283"/>
+      <x:c r="I283" t="str">
+        <x:v>K-35</x:v>
+      </x:c>
       <x:c r="J283"/>
       <x:c r="K283"/>
-      <x:c r="L283" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L283"/>
       <x:c r="M283"/>
       <x:c r="N283"/>
       <x:c r="O283"/>
@@ -13210,28 +13216,26 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B284" t="str">
-        <x:v>マンション</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C284" t="n">
         <x:v>285</x:v>
       </x:c>
       <x:c r="D284" t="n">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E284" t="str">
-        <x:v>幸福ハイツ</x:v>
+        <x:v>森辻牛舎</x:v>
       </x:c>
       <x:c r="F284"/>
-      <x:c r="G284" t="str">
-        <x:v>21-1160</x:v>
-      </x:c>
+      <x:c r="G284"/>
       <x:c r="H284"/>
-      <x:c r="I284"/>
+      <x:c r="I284" t="str">
+        <x:v>K-34</x:v>
+      </x:c>
       <x:c r="J284"/>
       <x:c r="K284"/>
-      <x:c r="L284" t="str">
-        <x:v>M-</x:v>
-      </x:c>
+      <x:c r="L284"/>
       <x:c r="M284"/>
       <x:c r="N284"/>
       <x:c r="O284"/>
@@ -13248,29 +13252,29 @@
         <x:v>緑ヶ丘</x:v>
       </x:c>
       <x:c r="B285" t="str">
-        <x:v>飲食　食品</x:v>
+        <x:v>マンション</x:v>
       </x:c>
       <x:c r="C285" t="n">
         <x:v>286</x:v>
       </x:c>
       <x:c r="D285" t="n">
-        <x:v>279</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E285" t="str">
-        <x:v>雅九</x:v>
+        <x:v>ルミエールA.B.C</x:v>
       </x:c>
       <x:c r="F285"/>
       <x:c r="G285"/>
       <x:c r="H285"/>
-      <x:c r="I285"/>
-      <x:c r="J285" t="str">
-        <x:v>K-19</x:v>
-      </x:c>
+      <x:c r="I285" t="str">
+        <x:v>K-31</x:v>
+      </x:c>
+      <x:c r="J285"/>
       <x:c r="K285"/>
-      <x:c r="L285"/>
-      <x:c r="M285" t="str">
-        <x:v>外-3</x:v>
-      </x:c>
+      <x:c r="L285" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="M285"/>
       <x:c r="N285"/>
       <x:c r="O285"/>
       <x:c r="P285"/>
@@ -13283,30 +13287,32 @@
     </x:row>
     <x:row r="286" ht="21" customHeight="1">
       <x:c r="A286" t="str">
-        <x:v>緑ヶ丘</x:v>
+        <x:v>夢が丘</x:v>
       </x:c>
       <x:c r="B286" t="str">
-        <x:v>官公庁</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C286" t="n">
         <x:v>287</x:v>
       </x:c>
       <x:c r="D286" t="n">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="E286" t="str">
-        <x:v>旧農業高校</x:v>
+        <x:v>前田商店</x:v>
       </x:c>
       <x:c r="F286"/>
       <x:c r="G286" t="str">
-        <x:v>24-0123</x:v>
-      </x:c>
-      <x:c r="H286"/>
-      <x:c r="I286" t="str">
-        <x:v>K-35</x:v>
-      </x:c>
+        <x:v>23-0168</x:v>
+      </x:c>
+      <x:c r="H286" t="str">
+        <x:v>H-5</x:v>
+      </x:c>
+      <x:c r="I286"/>
       <x:c r="J286"/>
-      <x:c r="K286"/>
+      <x:c r="K286" t="str">
+        <x:v>N-5</x:v>
+      </x:c>
       <x:c r="L286"/>
       <x:c r="M286"/>
       <x:c r="N286"/>
@@ -13321,7 +13327,7 @@
     </x:row>
     <x:row r="287" ht="21" customHeight="1">
       <x:c r="A287" t="str">
-        <x:v>緑ヶ丘</x:v>
+        <x:v>夢が丘</x:v>
       </x:c>
       <x:c r="B287" t="str">
         <x:v>会社　商店</x:v>
@@ -13330,20 +13336,24 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="D287" t="n">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E287" t="str">
-        <x:v>森辻牛舎</x:v>
+        <x:v>安永　夢が丘</x:v>
       </x:c>
       <x:c r="F287"/>
       <x:c r="G287"/>
-      <x:c r="H287"/>
-      <x:c r="I287" t="str">
-        <x:v>K-34</x:v>
-      </x:c>
-      <x:c r="J287"/>
+      <x:c r="H287" t="str">
+        <x:v>K-51</x:v>
+      </x:c>
+      <x:c r="I287"/>
+      <x:c r="J287" t="str">
+        <x:v>K-21</x:v>
+      </x:c>
       <x:c r="K287"/>
-      <x:c r="L287"/>
+      <x:c r="L287" t="str">
+        <x:v>K-1</x:v>
+      </x:c>
       <x:c r="M287"/>
       <x:c r="N287"/>
       <x:c r="O287"/>
@@ -13357,32 +13367,32 @@
     </x:row>
     <x:row r="288" ht="21" customHeight="1">
       <x:c r="A288" t="str">
-        <x:v>緑ヶ丘</x:v>
+        <x:v>夢が丘</x:v>
       </x:c>
       <x:c r="B288" t="str">
-        <x:v>マンション</x:v>
+        <x:v>新聞</x:v>
       </x:c>
       <x:c r="C288" t="n">
         <x:v>289</x:v>
       </x:c>
       <x:c r="D288" t="n">
-        <x:v>297</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E288" t="str">
-        <x:v>ルミエールA.B.C</x:v>
+        <x:v>読売新聞　上野中央</x:v>
       </x:c>
       <x:c r="F288"/>
-      <x:c r="G288"/>
+      <x:c r="G288" t="str">
+        <x:v>24-1638</x:v>
+      </x:c>
       <x:c r="H288"/>
-      <x:c r="I288" t="str">
-        <x:v>K-31</x:v>
-      </x:c>
+      <x:c r="I288"/>
       <x:c r="J288"/>
       <x:c r="K288"/>
-      <x:c r="L288" t="str">
-        <x:v>M-</x:v>
-      </x:c>
-      <x:c r="M288"/>
+      <x:c r="L288"/>
+      <x:c r="M288" t="str">
+        <x:v>外-1</x:v>
+      </x:c>
       <x:c r="N288"/>
       <x:c r="O288"/>
       <x:c r="P288"/>
@@ -13404,23 +13414,19 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="D289" t="n">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E289" t="str">
-        <x:v>前田商店</x:v>
+        <x:v>富士フィルムイノベーションジャパン</x:v>
       </x:c>
       <x:c r="F289"/>
-      <x:c r="G289" t="str">
-        <x:v>23-0168</x:v>
-      </x:c>
-      <x:c r="H289" t="str">
-        <x:v>H-5</x:v>
-      </x:c>
+      <x:c r="G289"/>
+      <x:c r="H289"/>
       <x:c r="I289"/>
-      <x:c r="J289"/>
-      <x:c r="K289" t="str">
-        <x:v>N-5</x:v>
-      </x:c>
+      <x:c r="J289" t="str">
+        <x:v>K-22</x:v>
+      </x:c>
+      <x:c r="K289"/>
       <x:c r="L289"/>
       <x:c r="M289"/>
       <x:c r="N289"/>
@@ -13433,35 +13439,35 @@
       <x:c r="U289"/>
       <x:c r="V289"/>
     </x:row>
-    <x:row r="290" ht="21" customHeight="1">
+    <x:row r="290" ht="22.5" customHeight="1">
       <x:c r="A290" t="str">
         <x:v>夢が丘</x:v>
       </x:c>
       <x:c r="B290" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>病院　薬</x:v>
       </x:c>
       <x:c r="C290" t="n">
         <x:v>291</x:v>
       </x:c>
       <x:c r="D290" t="n">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E290" t="str">
-        <x:v>安永　夢が丘</x:v>
+        <x:v>夢が丘薬局</x:v>
       </x:c>
       <x:c r="F290"/>
-      <x:c r="G290"/>
+      <x:c r="G290" t="str">
+        <x:v>41-0787</x:v>
+      </x:c>
       <x:c r="H290" t="str">
-        <x:v>K-51</x:v>
+        <x:v>K-52</x:v>
       </x:c>
       <x:c r="I290"/>
-      <x:c r="J290" t="str">
-        <x:v>K-21</x:v>
-      </x:c>
-      <x:c r="K290"/>
-      <x:c r="L290" t="str">
-        <x:v>K-1</x:v>
-      </x:c>
+      <x:c r="J290"/>
+      <x:c r="K290" t="str">
+        <x:v>N-1</x:v>
+      </x:c>
+      <x:c r="L290"/>
       <x:c r="M290"/>
       <x:c r="N290"/>
       <x:c r="O290"/>
@@ -13471,36 +13477,38 @@
       <x:c r="S290"/>
       <x:c r="T290"/>
       <x:c r="U290"/>
-      <x:c r="V290"/>
-    </x:row>
-    <x:row r="291" ht="21" customHeight="1">
+      <x:c r="V290" t="str">
+        <x:v>月昼、木朝一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="22.5" customHeight="1">
       <x:c r="A291" t="str">
         <x:v>夢が丘</x:v>
       </x:c>
       <x:c r="B291" t="str">
-        <x:v>新聞</x:v>
+        <x:v>公共施設</x:v>
       </x:c>
       <x:c r="C291" t="n">
         <x:v>292</x:v>
       </x:c>
       <x:c r="D291" t="n">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E291" t="str">
-        <x:v>読売新聞　上野中央</x:v>
+        <x:v>夢ドーム 日本環境マネージメント</x:v>
       </x:c>
       <x:c r="F291"/>
       <x:c r="G291" t="str">
-        <x:v>24-1638</x:v>
+        <x:v>22-0590</x:v>
       </x:c>
       <x:c r="H291"/>
       <x:c r="I291"/>
       <x:c r="J291"/>
-      <x:c r="K291"/>
+      <x:c r="K291" t="str">
+        <x:v>N-2</x:v>
+      </x:c>
       <x:c r="L291"/>
-      <x:c r="M291" t="str">
-        <x:v>外-1</x:v>
-      </x:c>
+      <x:c r="M291"/>
       <x:c r="N291"/>
       <x:c r="O291"/>
       <x:c r="P291"/>
@@ -13509,33 +13517,39 @@
       <x:c r="S291"/>
       <x:c r="T291"/>
       <x:c r="U291"/>
-      <x:c r="V291"/>
-    </x:row>
-    <x:row r="292" ht="21" customHeight="1">
+      <x:c r="V291" t="str">
+        <x:v>第２,4木曜</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
       <x:c r="A292" t="str">
-        <x:v>夢が丘</x:v>
+        <x:v>依那古</x:v>
       </x:c>
       <x:c r="B292" t="str">
-        <x:v>会社　商店</x:v>
+        <x:v>病院　薬</x:v>
       </x:c>
       <x:c r="C292" t="n">
         <x:v>293</x:v>
       </x:c>
       <x:c r="D292" t="n">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="E292" t="str">
-        <x:v>富士フィルムイノベーションジャパン</x:v>
+        <x:v>いなこ保険薬局</x:v>
       </x:c>
       <x:c r="F292"/>
-      <x:c r="G292"/>
+      <x:c r="G292" t="str">
+        <x:v>38-8555</x:v>
+      </x:c>
       <x:c r="H292"/>
-      <x:c r="I292"/>
-      <x:c r="J292" t="str">
-        <x:v>K-22</x:v>
-      </x:c>
+      <x:c r="I292" t="str">
+        <x:v>K-51</x:v>
+      </x:c>
+      <x:c r="J292"/>
       <x:c r="K292"/>
-      <x:c r="L292"/>
+      <x:c r="L292" t="str">
+        <x:v>K-56</x:v>
+      </x:c>
       <x:c r="M292"/>
       <x:c r="N292"/>
       <x:c r="O292"/>
@@ -13545,39 +13559,37 @@
       <x:c r="S292"/>
       <x:c r="T292"/>
       <x:c r="U292"/>
-      <x:c r="V292"/>
-    </x:row>
-    <x:row r="293" ht="22.5" customHeight="1">
+      <x:c r="V292" t="str">
+        <x:v>2時過ぎ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
       <x:c r="A293" t="str">
-        <x:v>夢が丘</x:v>
+        <x:v>依那古</x:v>
       </x:c>
       <x:c r="B293" t="str">
-        <x:v>病院　薬</x:v>
+        <x:v>会社　商店</x:v>
       </x:c>
       <x:c r="C293" t="n">
         <x:v>294</x:v>
       </x:c>
       <x:c r="D293" t="n">
-        <x:v>286</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E293" t="str">
-        <x:v>夢が丘薬局</x:v>
+        <x:v>会社の段ボール</x:v>
       </x:c>
       <x:c r="F293"/>
-      <x:c r="G293" t="str">
-        <x:v>41-0787</x:v>
-      </x:c>
-      <x:c r="H293" t="str">
-        <x:v>K-52</x:v>
-      </x:c>
+      <x:c r="G293"/>
+      <x:c r="H293"/>
       <x:c r="I293"/>
       <x:c r="J293"/>
-      <x:c r="K293" t="str">
-        <x:v>N-1</x:v>
-      </x:c>
+      <x:c r="K293"/>
       <x:c r="L293"/>
       <x:c r="M293"/>
-      <x:c r="N293"/>
+      <x:c r="N293" t="str">
+        <x:v>段紙(土)-1</x:v>
+      </x:c>
       <x:c r="O293"/>
       <x:c r="P293"/>
       <x:c r="Q293"/>
@@ -13585,39 +13597,35 @@
       <x:c r="S293"/>
       <x:c r="T293"/>
       <x:c r="U293"/>
-      <x:c r="V293" t="str">
-        <x:v>月昼、木朝一</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="294" ht="22.5" customHeight="1">
+      <x:c r="V293"/>
+    </x:row>
+    <x:row r="294">
       <x:c r="A294" t="str">
-        <x:v>夢が丘</x:v>
+        <x:v>四十九</x:v>
       </x:c>
       <x:c r="B294" t="str">
-        <x:v>公共施設</x:v>
+        <x:v>飲食　食品</x:v>
       </x:c>
       <x:c r="C294" t="n">
-        <x:v>295</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D294" t="n">
-        <x:v>287</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E294" t="str">
-        <x:v>夢ドーム 日本環境マネージメント</x:v>
+        <x:v>イオン PET・アルミ</x:v>
       </x:c>
       <x:c r="F294"/>
-      <x:c r="G294" t="str">
-        <x:v>22-0590</x:v>
-      </x:c>
+      <x:c r="G294"/>
       <x:c r="H294"/>
       <x:c r="I294"/>
       <x:c r="J294"/>
-      <x:c r="K294" t="str">
-        <x:v>N-2</x:v>
-      </x:c>
+      <x:c r="K294"/>
       <x:c r="L294"/>
       <x:c r="M294"/>
-      <x:c r="N294"/>
+      <x:c r="N294" t="str">
+        <x:v>段紙(土)-11</x:v>
+      </x:c>
       <x:c r="O294"/>
       <x:c r="P294"/>
       <x:c r="Q294"/>
@@ -13625,40 +13633,34 @@
       <x:c r="S294"/>
       <x:c r="T294"/>
       <x:c r="U294"/>
-      <x:c r="V294" t="str">
-        <x:v>第２,4木曜</x:v>
-      </x:c>
+      <x:c r="V294"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" t="str">
-        <x:v>依那古</x:v>
+        <x:v>四十九</x:v>
       </x:c>
       <x:c r="B295" t="str">
-        <x:v>病院　薬</x:v>
+        <x:v>買い物</x:v>
       </x:c>
       <x:c r="C295" t="n">
-        <x:v>296</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D295" t="n">
-        <x:v>288</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E295" t="str">
-        <x:v>いなこ保険薬局</x:v>
+        <x:v>クルーズ</x:v>
       </x:c>
       <x:c r="F295"/>
-      <x:c r="G295" t="str">
-        <x:v>38-8555</x:v>
-      </x:c>
+      <x:c r="G295"/>
       <x:c r="H295"/>
-      <x:c r="I295" t="str">
-        <x:v>K-51</x:v>
-      </x:c>
+      <x:c r="I295"/>
       <x:c r="J295"/>
       <x:c r="K295"/>
-      <x:c r="L295" t="str">
-        <x:v>K-56</x:v>
-      </x:c>
-      <x:c r="M295"/>
+      <x:c r="L295"/>
+      <x:c r="M295" t="str">
+        <x:v>外-16</x:v>
+      </x:c>
       <x:c r="N295"/>
       <x:c r="O295"/>
       <x:c r="P295"/>
@@ -13667,117 +13669,7 @@
       <x:c r="S295"/>
       <x:c r="T295"/>
       <x:c r="U295"/>
-      <x:c r="V295" t="str">
-        <x:v>2時過ぎ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="296">
-      <x:c r="A296" t="str">
-        <x:v>依那古</x:v>
-      </x:c>
-      <x:c r="B296" t="str">
-        <x:v>会社　商店</x:v>
-      </x:c>
-      <x:c r="C296" t="n">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="D296" t="n">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="E296" t="str">
-        <x:v>会社の段ボール</x:v>
-      </x:c>
-      <x:c r="F296"/>
-      <x:c r="G296"/>
-      <x:c r="H296"/>
-      <x:c r="I296"/>
-      <x:c r="J296"/>
-      <x:c r="K296"/>
-      <x:c r="L296"/>
-      <x:c r="M296"/>
-      <x:c r="N296" t="str">
-        <x:v>段紙(土)-1</x:v>
-      </x:c>
-      <x:c r="O296"/>
-      <x:c r="P296"/>
-      <x:c r="Q296"/>
-      <x:c r="R296"/>
-      <x:c r="S296"/>
-      <x:c r="T296"/>
-      <x:c r="U296"/>
-      <x:c r="V296"/>
-    </x:row>
-    <x:row r="297">
-      <x:c r="A297" t="str">
-        <x:v>四十九</x:v>
-      </x:c>
-      <x:c r="B297" t="str">
-        <x:v>飲食　食品</x:v>
-      </x:c>
-      <x:c r="C297" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D297" t="n">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="E297" t="str">
-        <x:v>イオン PET・アルミ</x:v>
-      </x:c>
-      <x:c r="F297"/>
-      <x:c r="G297"/>
-      <x:c r="H297"/>
-      <x:c r="I297"/>
-      <x:c r="J297"/>
-      <x:c r="K297"/>
-      <x:c r="L297"/>
-      <x:c r="M297"/>
-      <x:c r="N297" t="str">
-        <x:v>段紙(土)-11</x:v>
-      </x:c>
-      <x:c r="O297"/>
-      <x:c r="P297"/>
-      <x:c r="Q297"/>
-      <x:c r="R297"/>
-      <x:c r="S297"/>
-      <x:c r="T297"/>
-      <x:c r="U297"/>
-      <x:c r="V297"/>
-    </x:row>
-    <x:row r="298">
-      <x:c r="A298" t="str">
-        <x:v>四十九</x:v>
-      </x:c>
-      <x:c r="B298" t="str">
-        <x:v>買い物</x:v>
-      </x:c>
-      <x:c r="C298" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D298" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="E298" t="str">
-        <x:v>クルーズ</x:v>
-      </x:c>
-      <x:c r="F298"/>
-      <x:c r="G298"/>
-      <x:c r="H298"/>
-      <x:c r="I298"/>
-      <x:c r="J298"/>
-      <x:c r="K298"/>
-      <x:c r="L298"/>
-      <x:c r="M298" t="str">
-        <x:v>外-16</x:v>
-      </x:c>
-      <x:c r="N298"/>
-      <x:c r="O298"/>
-      <x:c r="P298"/>
-      <x:c r="Q298"/>
-      <x:c r="R298"/>
-      <x:c r="S298"/>
-      <x:c r="T298"/>
-      <x:c r="U298"/>
-      <x:c r="V298"/>
+      <x:c r="V295"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26118,6 +26010,138 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>上ノ庄</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>会社　商店</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>東研サーモテック</x:v>
+      </x:c>
+      <x:c r="F4"/>
+      <x:c r="G4" t="str">
+        <x:v>63-5321</x:v>
+      </x:c>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
+      <x:c r="Q4"/>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c t="str" r="V4">
+        <x:v>物件表</x:v>
+      </x:c>
+      <x:c t="n" r="W4">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c t="n" r="X4">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>緑ヶ丘</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>飲食　食品</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>michi</x:v>
+      </x:c>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
+      <x:c t="str" r="V5">
+        <x:v>物件表</x:v>
+      </x:c>
+      <x:c t="n" r="W5">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c t="n" r="X5">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>緑ヶ丘</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>ヘアカット</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>ソレイユ緑ヶ丘店</x:v>
+      </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6" t="str">
+        <x:v>21-3754</x:v>
+      </x:c>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
+      <x:c r="Q6"/>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c t="str" r="V6">
+        <x:v>物件表</x:v>
+      </x:c>
+      <x:c t="n" r="W6">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c t="n" r="X6">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -9928,7 +9928,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>金属-64</t>
+          <t>金属-63</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>金属-63</t>
+          <t>金属-62</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>金属-62</t>
+          <t>金属-61</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>金属-65</t>
+          <t>金属-64</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>金属-58</t>
+          <t>金属-57</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>金属-60</t>
+          <t>金属-59</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>金属-61</t>
+          <t>金属-60</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>金属-59</t>
+          <t>金属-58</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -10521,11 +10521,6 @@
       <c r="K239" t="inlineStr">
         <is>
           <t>K-34</t>
-        </is>
-      </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>金属-54</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -9571,6 +9571,11 @@
           <t>K-6</t>
         </is>
       </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>金属-65</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="21" customHeight="1" s="10">
       <c r="A216" t="inlineStr">

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -1793,6 +1793,11 @@
           <t>M-</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>金属-</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>段紙-5</t>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>金属-6</t>
+          <t>金属-7</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>金属-</t>
+          <t>金属-6</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>金属-19</t>
+          <t>金属-20</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>金属-20</t>
+          <t>金属-21</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>金属-22</t>
+          <t>金属-23</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>金属-21</t>
+          <t>金属-22</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>金属-23</t>
+          <t>金属-24</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>金属-24</t>
+          <t>金属-25</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>金属-25</t>
+          <t>金属-26</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>金属-29</t>
+          <t>金属-30</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>金属-28</t>
+          <t>金属-29</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>金属-30</t>
+          <t>金属-31</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>金属-27</t>
+          <t>金属-28</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>金属-26</t>
+          <t>金属-27</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>金属-31</t>
+          <t>金属-32</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>金属-33</t>
+          <t>金属-34</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>金属-32</t>
+          <t>金属-33</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>金属-34</t>
+          <t>金属-35</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>金属-35</t>
+          <t>金属-36</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>金属-36</t>
+          <t>金属-37</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>金属-37</t>
+          <t>金属-38</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>金属-38</t>
+          <t>金属-39</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>金属-40</t>
+          <t>金属-41</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>金属-41</t>
+          <t>金属-42</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>金属-42</t>
+          <t>金属-43</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>金属-43</t>
+          <t>金属-44</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>金属-39</t>
+          <t>金属-40</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>金属-44</t>
+          <t>金属-45</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>金属-45</t>
+          <t>金属-46</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>金属-46</t>
+          <t>金属-47</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>金属-47</t>
+          <t>金属-48</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>金属-48</t>
+          <t>金属-49</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>金属-49</t>
+          <t>金属-50</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>金属-50</t>
+          <t>金属-51</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>金属-52</t>
+          <t>金属-53</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>金属-51</t>
+          <t>金属-52</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>金属-53</t>
+          <t>金属-54</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>金属-54</t>
+          <t>金属-55</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>金属-55</t>
+          <t>金属-56</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>金属-65</t>
+          <t>金属-66</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>金属-63</t>
+          <t>金属-64</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>金属-62</t>
+          <t>金属-63</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>金属-61</t>
+          <t>金属-62</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>金属-64</t>
+          <t>金属-65</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>金属-57</t>
+          <t>金属-58</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>金属-59</t>
+          <t>金属-60</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>金属-60</t>
+          <t>金属-61</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>金属-58</t>
+          <t>金属-59</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>金属-56</t>
+          <t>金属-57</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>金属-14</t>
+          <t>金属-15</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>金属-15</t>
+          <t>金属-16</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>金属-17</t>
+          <t>金属-18</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>金属-18</t>
+          <t>金属-19</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>金属-16</t>
+          <t>金属-17</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>金属-13</t>
+          <t>金属-14</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>金属-12</t>
+          <t>金属-13</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>金属-11</t>
+          <t>金属-12</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>金属-8</t>
+          <t>金属-9</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>金属-7</t>
+          <t>金属-8</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>金属-10</t>
+          <t>金属-11</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>金属-9</t>
+          <t>金属-10</t>
         </is>
       </c>
     </row>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -8560,12 +8560,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>上野上柘植トラックセンター</t>
+          <t>One Road 上柘植トラックセンター</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
           <t>45-8877</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>第1第3水曜日</t>
         </is>
       </c>
     </row>

--- a/許可物件表_Git.xlsx
+++ b/許可物件表_Git.xlsx
@@ -6446,6 +6446,11 @@
           <t>N-32</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>N-33</t>
